--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 бррсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 бррсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\15,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDFFECC-2C81-4D5C-AC6B-FA4467D3F4BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B01CF4A-E030-497D-BD33-A715CAF21BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AP$132</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -725,7 +717,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -772,6 +764,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -808,7 +812,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -833,13 +837,14 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -859,7 +864,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -7023,7 +7028,7 @@
   <dimension ref="A1:AY499"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="49.5703125" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
     <col min="3" max="4" width="6" customWidth="1"/>
     <col min="5" max="6" width="7" customWidth="1"/>
@@ -7036,13 +7041,14 @@
     <col min="15" max="16" width="7" customWidth="1"/>
     <col min="17" max="17" width="6.42578125" style="24" customWidth="1"/>
     <col min="18" max="26" width="7" customWidth="1"/>
-    <col min="27" max="27" width="7" style="26" customWidth="1"/>
-    <col min="28" max="28" width="7.42578125" style="26" customWidth="1"/>
+    <col min="27" max="27" width="7" style="25" customWidth="1"/>
+    <col min="28" max="28" width="5.42578125" style="25" customWidth="1"/>
     <col min="29" max="30" width="5" customWidth="1"/>
     <col min="31" max="40" width="6" customWidth="1"/>
-    <col min="41" max="41" width="11.28515625" customWidth="1"/>
+    <col min="41" max="41" width="5.85546875" customWidth="1"/>
     <col min="42" max="42" width="7" customWidth="1"/>
-    <col min="43" max="51" width="3" customWidth="1"/>
+    <col min="43" max="44" width="6.140625" customWidth="1"/>
+    <col min="45" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
@@ -7062,7 +7068,7 @@
       <c r="N1" s="15"/>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
-      <c r="Q1" s="28" t="s">
+      <c r="Q1" s="27" t="s">
         <v>189</v>
       </c>
       <c r="R1" s="15"/>
@@ -7073,7 +7079,7 @@
       <c r="W1" s="15"/>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
-      <c r="Z1" s="27">
+      <c r="Z1" s="26">
         <v>1.8</v>
       </c>
       <c r="AA1" s="15"/>
@@ -7119,7 +7125,7 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
-      <c r="Q2" s="28"/>
+      <c r="Q2" s="27"/>
       <c r="R2" s="15"/>
       <c r="S2" s="15"/>
       <c r="T2" s="15"/>
@@ -7336,7 +7342,7 @@
       <c r="W4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="X4" s="29" t="s">
         <v>30</v>
       </c>
       <c r="Y4" s="15"/>
@@ -7349,7 +7355,7 @@
       <c r="AB4" s="15"/>
       <c r="AC4" s="15"/>
       <c r="AD4" s="15"/>
-      <c r="AE4" s="15" t="s">
+      <c r="AE4" s="28" t="s">
         <v>31</v>
       </c>
       <c r="AF4" s="15" t="s">
@@ -7381,8 +7387,8 @@
       </c>
       <c r="AO4" s="15"/>
       <c r="AP4" s="15"/>
-      <c r="AQ4" s="15"/>
-      <c r="AR4" s="15"/>
+      <c r="AQ4" s="29"/>
+      <c r="AR4" s="28"/>
       <c r="AS4" s="15"/>
       <c r="AT4" s="15"/>
       <c r="AU4" s="15"/>
@@ -7521,8 +7527,14 @@
         <f>SUM(AP6:AP499)</f>
         <v>9155</v>
       </c>
-      <c r="AQ5" s="15"/>
-      <c r="AR5" s="15"/>
+      <c r="AQ5" s="3">
+        <f>SUM(AQ6:AQ499)</f>
+        <v>2571.7304000000004</v>
+      </c>
+      <c r="AR5" s="3">
+        <f>SUM(AR6:AR499)</f>
+        <v>3255.7598199999998</v>
+      </c>
       <c r="AS5" s="15"/>
       <c r="AT5" s="15"/>
       <c r="AU5" s="15"/>
@@ -7594,11 +7606,11 @@
         <f>AA6</f>
         <v>150</v>
       </c>
-      <c r="AA6" s="25">
+      <c r="AA6" s="15">
         <f>VLOOKUP(A6,[1]Sheet!$A:$AA,26,0)</f>
         <v>150</v>
       </c>
-      <c r="AB6" s="25" t="str">
+      <c r="AB6" s="15" t="str">
         <f>VLOOKUP(A6,[1]Sheet!$A:$AA,27,0)</f>
         <v>Промо</v>
       </c>
@@ -7645,8 +7657,14 @@
         <f>ROUND(G6*Z6,0)</f>
         <v>150</v>
       </c>
-      <c r="AQ6" s="15"/>
-      <c r="AR6" s="15"/>
+      <c r="AQ6" s="15">
+        <f>X6*G6</f>
+        <v>50.513600000000004</v>
+      </c>
+      <c r="AR6" s="15">
+        <f>AE6*G6</f>
+        <v>52.347000000000001</v>
+      </c>
       <c r="AS6" s="15"/>
       <c r="AT6" s="15"/>
       <c r="AU6" s="15"/>
@@ -7718,8 +7736,8 @@
         <f>Y7+X7*$Z$1</f>
         <v>370.68672000000026</v>
       </c>
-      <c r="AA7" s="25"/>
-      <c r="AB7" s="25"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
       <c r="AC7" s="15">
         <f t="shared" ref="AC7:AC70" si="5">(F7+O7+P7+Q7+R7+S7+T7+U7+V7+W7+Z7)/X7</f>
         <v>12.8</v>
@@ -7763,8 +7781,14 @@
         <f t="shared" ref="AP7:AP70" si="6">ROUND(G7*Z7,0)</f>
         <v>371</v>
       </c>
-      <c r="AQ7" s="15"/>
-      <c r="AR7" s="15"/>
+      <c r="AQ7" s="15">
+        <f t="shared" ref="AQ7:AQ70" si="7">X7*G7</f>
+        <v>102.57940000000001</v>
+      </c>
+      <c r="AR7" s="15">
+        <f t="shared" ref="AR7:AR70" si="8">AE7*G7</f>
+        <v>91.360199999999992</v>
+      </c>
       <c r="AS7" s="15"/>
       <c r="AT7" s="15"/>
       <c r="AU7" s="15"/>
@@ -7830,11 +7854,11 @@
       </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4">
-        <f t="shared" ref="Z8:Z66" si="7">Y8</f>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
+        <f t="shared" ref="Z8:Z66" si="9">Y8</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
       <c r="AC8" s="15">
         <f t="shared" si="5"/>
         <v>14.649195381166148</v>
@@ -7878,8 +7902,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ8" s="15"/>
-      <c r="AR8" s="15"/>
+      <c r="AQ8" s="15">
+        <f t="shared" si="7"/>
+        <v>78.322800000000001</v>
+      </c>
+      <c r="AR8" s="15">
+        <f t="shared" si="8"/>
+        <v>84.352599999999995</v>
+      </c>
       <c r="AS8" s="15"/>
       <c r="AT8" s="15"/>
       <c r="AU8" s="15"/>
@@ -7933,11 +7963,11 @@
       </c>
       <c r="Y9" s="13"/>
       <c r="Z9" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
       <c r="AC9" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -7983,8 +8013,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ9" s="15"/>
-      <c r="AR9" s="15"/>
+      <c r="AQ9" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR9" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AS9" s="15"/>
       <c r="AT9" s="15"/>
       <c r="AU9" s="15"/>
@@ -8050,11 +8086,11 @@
       </c>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
       <c r="AC10" s="15">
         <f t="shared" si="5"/>
         <v>17.403902356902361</v>
@@ -8098,8 +8134,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ10" s="15"/>
-      <c r="AR10" s="15"/>
+      <c r="AQ10" s="15">
+        <f t="shared" si="7"/>
+        <v>26.73</v>
+      </c>
+      <c r="AR10" s="15">
+        <f t="shared" si="8"/>
+        <v>36.04842</v>
+      </c>
       <c r="AS10" s="15"/>
       <c r="AT10" s="15"/>
       <c r="AU10" s="15"/>
@@ -8165,11 +8207,11 @@
       </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="15"/>
       <c r="AC11" s="15">
         <f t="shared" si="5"/>
         <v>73.89705882352942</v>
@@ -8215,8 +8257,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ11" s="15"/>
-      <c r="AR11" s="15"/>
+      <c r="AQ11" s="15">
+        <f t="shared" si="7"/>
+        <v>12.24</v>
+      </c>
+      <c r="AR11" s="15">
+        <f t="shared" si="8"/>
+        <v>42.84</v>
+      </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
       <c r="AU11" s="15"/>
@@ -8284,11 +8332,11 @@
       <c r="Z12" s="4">
         <v>60</v>
       </c>
-      <c r="AA12" s="25">
+      <c r="AA12" s="15">
         <f>VLOOKUP(A12,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB12" s="25" t="str">
+      <c r="AB12" s="15" t="str">
         <f>VLOOKUP(A12,[1]Sheet!$A:$AA,27,0)</f>
         <v>Хорошие сроки, продукт востребован в данном регионе т.к. ситуация со светом не стабильна</v>
       </c>
@@ -8335,8 +8383,14 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="AQ12" s="15"/>
-      <c r="AR12" s="15"/>
+      <c r="AQ12" s="15">
+        <f t="shared" si="7"/>
+        <v>1.4280000000000002</v>
+      </c>
+      <c r="AR12" s="15">
+        <f t="shared" si="8"/>
+        <v>1.53</v>
+      </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
       <c r="AU12" s="15"/>
@@ -8402,14 +8456,14 @@
       </c>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4">
-        <f t="shared" ref="Z13:Z15" si="8">AA13</f>
+        <f t="shared" ref="Z13:Z15" si="10">AA13</f>
         <v>60</v>
       </c>
-      <c r="AA13" s="25">
+      <c r="AA13" s="15">
         <f>VLOOKUP(A13,[1]Sheet!$A:$AA,26,0)</f>
         <v>60</v>
       </c>
-      <c r="AB13" s="25" t="str">
+      <c r="AB13" s="15" t="str">
         <f>VLOOKUP(A13,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -8456,8 +8510,14 @@
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="AQ13" s="15"/>
-      <c r="AR13" s="15"/>
+      <c r="AQ13" s="15">
+        <f t="shared" si="7"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="AR13" s="15">
+        <f t="shared" si="8"/>
+        <v>3.42</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
       <c r="AU13" s="15"/>
@@ -8523,14 +8583,14 @@
       </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AA14" s="25">
+      <c r="AA14" s="15">
         <f>VLOOKUP(A14,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB14" s="25" t="str">
+      <c r="AB14" s="15" t="str">
         <f>VLOOKUP(A14,[1]Sheet!$A:$AA,27,0)</f>
         <v>Хорошие сроки, продукт востребован в данном регионе т.к. ситуация со светом не стабильна</v>
       </c>
@@ -8577,8 +8637,14 @@
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="AQ14" s="15"/>
-      <c r="AR14" s="15"/>
+      <c r="AQ14" s="15">
+        <f t="shared" si="7"/>
+        <v>7.2759999999999998</v>
+      </c>
+      <c r="AR14" s="15">
+        <f t="shared" si="8"/>
+        <v>9.4520000000000017</v>
+      </c>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
       <c r="AU14" s="15"/>
@@ -8647,14 +8713,14 @@
         <v>138.78099999999995</v>
       </c>
       <c r="Z15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>270</v>
       </c>
-      <c r="AA15" s="25">
+      <c r="AA15" s="15">
         <f>VLOOKUP(A15,[1]Sheet!$A:$AA,26,0)</f>
         <v>270</v>
       </c>
-      <c r="AB15" s="25" t="str">
+      <c r="AB15" s="15" t="str">
         <f>VLOOKUP(A15,[1]Sheet!$A:$AA,27,0)</f>
         <v>Промо и сроки хорошие</v>
       </c>
@@ -8701,8 +8767,14 @@
         <f t="shared" si="6"/>
         <v>270</v>
       </c>
-      <c r="AQ15" s="15"/>
-      <c r="AR15" s="15"/>
+      <c r="AQ15" s="15">
+        <f t="shared" si="7"/>
+        <v>92.775999999999996</v>
+      </c>
+      <c r="AR15" s="15">
+        <f t="shared" si="8"/>
+        <v>91.034000000000006</v>
+      </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
       <c r="AU15" s="15"/>
@@ -8775,8 +8847,8 @@
         <f>Y16+X16*$Z$1</f>
         <v>787.5626400000001</v>
       </c>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="25"/>
+      <c r="AA16" s="15"/>
+      <c r="AB16" s="15"/>
       <c r="AC16" s="15">
         <f t="shared" si="5"/>
         <v>12.972005061083141</v>
@@ -8820,8 +8892,14 @@
         <f t="shared" si="6"/>
         <v>788</v>
       </c>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
+      <c r="AQ16" s="15">
+        <f t="shared" si="7"/>
+        <v>437.53480000000002</v>
+      </c>
+      <c r="AR16" s="15">
+        <f t="shared" si="8"/>
+        <v>456.43400000000003</v>
+      </c>
       <c r="AS16" s="15"/>
       <c r="AT16" s="15"/>
       <c r="AU16" s="15"/>
@@ -8887,11 +8965,11 @@
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
       <c r="AC17" s="15">
         <f t="shared" si="5"/>
         <v>13.339283816810113</v>
@@ -8935,8 +9013,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="15"/>
-      <c r="AR17" s="15"/>
+      <c r="AQ17" s="15">
+        <f t="shared" si="7"/>
+        <v>11.293200000000001</v>
+      </c>
+      <c r="AR17" s="15">
+        <f t="shared" si="8"/>
+        <v>15.170199999999999</v>
+      </c>
       <c r="AS17" s="15"/>
       <c r="AT17" s="15"/>
       <c r="AU17" s="15"/>
@@ -8996,11 +9080,11 @@
       </c>
       <c r="Y18" s="13"/>
       <c r="Z18" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="25"/>
-      <c r="AB18" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
       <c r="AC18" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -9044,8 +9128,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
+      <c r="AQ18" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AS18" s="15"/>
       <c r="AT18" s="15"/>
       <c r="AU18" s="15"/>
@@ -9114,8 +9204,8 @@
         <f>Y19*1.5</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="25"/>
-      <c r="AB19" s="25"/>
+      <c r="AA19" s="15"/>
+      <c r="AB19" s="15"/>
       <c r="AC19" s="15">
         <f t="shared" si="5"/>
         <v>14.328799693212318</v>
@@ -9159,8 +9249,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ19" s="15"/>
-      <c r="AR19" s="15"/>
+      <c r="AQ19" s="15">
+        <f t="shared" si="7"/>
+        <v>7.8230000000000004</v>
+      </c>
+      <c r="AR19" s="15">
+        <f t="shared" si="8"/>
+        <v>10.795400000000001</v>
+      </c>
       <c r="AS19" s="15"/>
       <c r="AT19" s="15"/>
       <c r="AU19" s="15"/>
@@ -9229,11 +9325,11 @@
         <f>AA20</f>
         <v>35</v>
       </c>
-      <c r="AA20" s="25">
+      <c r="AA20" s="15">
         <f>VLOOKUP(A20,[1]Sheet!$A:$AA,26,0)</f>
         <v>35</v>
       </c>
-      <c r="AB20" s="25" t="str">
+      <c r="AB20" s="15" t="str">
         <f>VLOOKUP(A20,[1]Sheet!$A:$AA,27,0)</f>
         <v>Хорошие сроки, продукт востребован в данном регионе т.к. ситуация со светом не стабильна</v>
       </c>
@@ -9280,8 +9376,14 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="AQ20" s="15"/>
-      <c r="AR20" s="15"/>
+      <c r="AQ20" s="15">
+        <f t="shared" si="7"/>
+        <v>5.5602</v>
+      </c>
+      <c r="AR20" s="15">
+        <f t="shared" si="8"/>
+        <v>7.5060000000000002</v>
+      </c>
       <c r="AS20" s="15"/>
       <c r="AT20" s="15"/>
       <c r="AU20" s="15"/>
@@ -9347,11 +9449,11 @@
       </c>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="15"/>
       <c r="AC21" s="15">
         <f t="shared" si="5"/>
         <v>16.775953894576585</v>
@@ -9395,8 +9497,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ21" s="15"/>
-      <c r="AR21" s="15"/>
+      <c r="AQ21" s="15">
+        <f t="shared" si="7"/>
+        <v>56.750199999999992</v>
+      </c>
+      <c r="AR21" s="15">
+        <f t="shared" si="8"/>
+        <v>79.769800000000004</v>
+      </c>
       <c r="AS21" s="15"/>
       <c r="AT21" s="15"/>
       <c r="AU21" s="15"/>
@@ -9465,14 +9573,14 @@
         <v>30.222799999999999</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" ref="Z22:Z24" si="9">AA22</f>
+        <f t="shared" ref="Z22:Z24" si="11">AA22</f>
         <v>140</v>
       </c>
-      <c r="AA22" s="25">
+      <c r="AA22" s="15">
         <f>VLOOKUP(A22,[1]Sheet!$A:$AA,26,0)</f>
         <v>140</v>
       </c>
-      <c r="AB22" s="25" t="str">
+      <c r="AB22" s="15" t="str">
         <f>VLOOKUP(A22,[1]Sheet!$A:$AA,27,0)</f>
         <v>Промо и сроки хорошие</v>
       </c>
@@ -9519,8 +9627,14 @@
         <f t="shared" si="6"/>
         <v>140</v>
       </c>
-      <c r="AQ22" s="15"/>
-      <c r="AR22" s="15"/>
+      <c r="AQ22" s="15">
+        <f t="shared" si="7"/>
+        <v>24.557600000000001</v>
+      </c>
+      <c r="AR22" s="15">
+        <f t="shared" si="8"/>
+        <v>24.7864</v>
+      </c>
       <c r="AS22" s="15"/>
       <c r="AT22" s="15"/>
       <c r="AU22" s="15"/>
@@ -9586,14 +9700,14 @@
       </c>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AA23" s="25">
+      <c r="AA23" s="15">
         <f>VLOOKUP(A23,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB23" s="25" t="str">
+      <c r="AB23" s="15" t="str">
         <f>VLOOKUP(A23,[1]Sheet!$A:$AA,27,0)</f>
         <v>Промо и сроки хорошие</v>
       </c>
@@ -9642,8 +9756,14 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AQ23" s="15"/>
-      <c r="AR23" s="15"/>
+      <c r="AQ23" s="15">
+        <f t="shared" si="7"/>
+        <v>18.269200000000001</v>
+      </c>
+      <c r="AR23" s="15">
+        <f t="shared" si="8"/>
+        <v>21.5534</v>
+      </c>
       <c r="AS23" s="15"/>
       <c r="AT23" s="15"/>
       <c r="AU23" s="15"/>
@@ -9709,14 +9829,14 @@
       </c>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>35</v>
       </c>
-      <c r="AA24" s="25">
+      <c r="AA24" s="15">
         <f>VLOOKUP(A24,[1]Sheet!$A:$AA,26,0)</f>
         <v>35</v>
       </c>
-      <c r="AB24" s="25" t="str">
+      <c r="AB24" s="15" t="str">
         <f>VLOOKUP(A24,[1]Sheet!$A:$AA,27,0)</f>
         <v>Хорошие сроки, продукт востребован в данном регионе т.к. ситуация со светом не стабильна</v>
       </c>
@@ -9763,8 +9883,14 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="AQ24" s="15"/>
-      <c r="AR24" s="15"/>
+      <c r="AQ24" s="15">
+        <f t="shared" si="7"/>
+        <v>6.7364000000000006</v>
+      </c>
+      <c r="AR24" s="15">
+        <f t="shared" si="8"/>
+        <v>8.1237999999999992</v>
+      </c>
       <c r="AS24" s="15"/>
       <c r="AT24" s="15"/>
       <c r="AU24" s="15"/>
@@ -9836,8 +9962,8 @@
         <f>Y25*1.5</f>
         <v>303.96300000000002</v>
       </c>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
       <c r="AC25" s="15">
         <f t="shared" si="5"/>
         <v>12.991450135618539</v>
@@ -9883,8 +10009,14 @@
         <f t="shared" si="6"/>
         <v>304</v>
       </c>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="AQ25" s="15">
+        <f t="shared" si="7"/>
+        <v>50.878</v>
+      </c>
+      <c r="AR25" s="15">
+        <f t="shared" si="8"/>
+        <v>32.047199999999997</v>
+      </c>
       <c r="AS25" s="15"/>
       <c r="AT25" s="15"/>
       <c r="AU25" s="15"/>
@@ -9940,11 +10072,11 @@
       </c>
       <c r="Y26" s="13"/>
       <c r="Z26" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA26" s="25"/>
-      <c r="AB26" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="15"/>
       <c r="AC26" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -9990,8 +10122,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ26" s="15"/>
-      <c r="AR26" s="15"/>
+      <c r="AQ26" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR26" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AS26" s="15"/>
       <c r="AT26" s="15"/>
       <c r="AU26" s="15"/>
@@ -10061,8 +10199,8 @@
         <f>Y27*1.5</f>
         <v>26.337299999999999</v>
       </c>
-      <c r="AA27" s="25"/>
-      <c r="AB27" s="25"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
       <c r="AC27" s="15">
         <f t="shared" si="5"/>
         <v>11.480804197336138</v>
@@ -10106,8 +10244,14 @@
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="AQ27" s="15"/>
-      <c r="AR27" s="15"/>
+      <c r="AQ27" s="15">
+        <f t="shared" si="7"/>
+        <v>18.2592</v>
+      </c>
+      <c r="AR27" s="15">
+        <f t="shared" si="8"/>
+        <v>16.141200000000001</v>
+      </c>
       <c r="AS27" s="15"/>
       <c r="AT27" s="15"/>
       <c r="AU27" s="15"/>
@@ -10178,11 +10322,11 @@
         <f>AA28</f>
         <v>80</v>
       </c>
-      <c r="AA28" s="25">
+      <c r="AA28" s="15">
         <f>VLOOKUP(A28,[1]Sheet!$A:$AA,26,0)</f>
         <v>80</v>
       </c>
-      <c r="AB28" s="25" t="str">
+      <c r="AB28" s="15" t="str">
         <f>VLOOKUP(A28,[1]Sheet!$A:$AA,27,0)</f>
         <v>Спрос.</v>
       </c>
@@ -10229,8 +10373,14 @@
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="AQ28" s="15"/>
-      <c r="AR28" s="15"/>
+      <c r="AQ28" s="15">
+        <f t="shared" si="7"/>
+        <v>8.9708000000000006</v>
+      </c>
+      <c r="AR28" s="15">
+        <f t="shared" si="8"/>
+        <v>-0.30919999999999997</v>
+      </c>
       <c r="AS28" s="15"/>
       <c r="AT28" s="15"/>
       <c r="AU28" s="15"/>
@@ -10301,8 +10451,8 @@
         <f>Y29*1.5</f>
         <v>300</v>
       </c>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15"/>
       <c r="AC29" s="15">
         <f t="shared" si="5"/>
         <v>17.090320035205391</v>
@@ -10348,8 +10498,14 @@
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="AQ29" s="15"/>
-      <c r="AR29" s="15"/>
+      <c r="AQ29" s="15">
+        <f t="shared" si="7"/>
+        <v>39.539400000000001</v>
+      </c>
+      <c r="AR29" s="15">
+        <f t="shared" si="8"/>
+        <v>40.031599999999997</v>
+      </c>
       <c r="AS29" s="15"/>
       <c r="AT29" s="15"/>
       <c r="AU29" s="15"/>
@@ -10420,11 +10576,11 @@
         <f>AA30</f>
         <v>300</v>
       </c>
-      <c r="AA30" s="25">
+      <c r="AA30" s="15">
         <f>VLOOKUP(A30,[1]Sheet!$A:$AA,26,0)</f>
         <v>300</v>
       </c>
-      <c r="AB30" s="25" t="str">
+      <c r="AB30" s="15" t="str">
         <f>VLOOKUP(A30,[1]Sheet!$A:$AA,27,0)</f>
         <v>Спрос.</v>
       </c>
@@ -10473,8 +10629,14 @@
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="AQ30" s="15"/>
-      <c r="AR30" s="15"/>
+      <c r="AQ30" s="15">
+        <f t="shared" si="7"/>
+        <v>65.6066</v>
+      </c>
+      <c r="AR30" s="15">
+        <f t="shared" si="8"/>
+        <v>148.5498</v>
+      </c>
       <c r="AS30" s="15"/>
       <c r="AT30" s="15"/>
       <c r="AU30" s="15"/>
@@ -10546,8 +10708,8 @@
         <f>Y31*1.5</f>
         <v>57.9636</v>
       </c>
-      <c r="AA31" s="25"/>
-      <c r="AB31" s="25"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
       <c r="AC31" s="15">
         <f t="shared" si="5"/>
         <v>14.374056999161777</v>
@@ -10591,8 +10753,14 @@
         <f t="shared" si="6"/>
         <v>58</v>
       </c>
-      <c r="AQ31" s="15"/>
-      <c r="AR31" s="15"/>
+      <c r="AQ31" s="15">
+        <f t="shared" si="7"/>
+        <v>5.7263999999999999</v>
+      </c>
+      <c r="AR31" s="15">
+        <f t="shared" si="8"/>
+        <v>3.5457999999999998</v>
+      </c>
       <c r="AS31" s="15"/>
       <c r="AT31" s="15"/>
       <c r="AU31" s="15"/>
@@ -10658,11 +10826,11 @@
       </c>
       <c r="Y32" s="4"/>
       <c r="Z32" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA32" s="25"/>
-      <c r="AB32" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA32" s="15"/>
+      <c r="AB32" s="15"/>
       <c r="AC32" s="15">
         <f t="shared" si="5"/>
         <v>32.81139601139602</v>
@@ -10708,8 +10876,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ32" s="15"/>
-      <c r="AR32" s="15"/>
+      <c r="AQ32" s="15">
+        <f t="shared" si="7"/>
+        <v>7.7219999999999995</v>
+      </c>
+      <c r="AR32" s="15">
+        <f t="shared" si="8"/>
+        <v>20.628799999999998</v>
+      </c>
       <c r="AS32" s="15"/>
       <c r="AT32" s="15"/>
       <c r="AU32" s="15"/>
@@ -10782,8 +10956,8 @@
         <f>Y33*1.5</f>
         <v>225</v>
       </c>
-      <c r="AA33" s="25"/>
-      <c r="AB33" s="25"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
       <c r="AC33" s="15">
         <f t="shared" si="5"/>
         <v>12.866448319396923</v>
@@ -10829,8 +11003,14 @@
         <f t="shared" si="6"/>
         <v>225</v>
       </c>
-      <c r="AQ33" s="15"/>
-      <c r="AR33" s="15"/>
+      <c r="AQ33" s="15">
+        <f t="shared" si="7"/>
+        <v>21.8612</v>
+      </c>
+      <c r="AR33" s="15">
+        <f t="shared" si="8"/>
+        <v>24.236000000000001</v>
+      </c>
       <c r="AS33" s="15"/>
       <c r="AT33" s="15"/>
       <c r="AU33" s="15"/>
@@ -10886,11 +11066,11 @@
       </c>
       <c r="Y34" s="13"/>
       <c r="Z34" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="15"/>
       <c r="AC34" s="15">
         <f t="shared" si="5"/>
         <v>-5</v>
@@ -10934,8 +11114,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ34" s="15"/>
-      <c r="AR34" s="15"/>
+      <c r="AQ34" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR34" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AS34" s="15"/>
       <c r="AT34" s="15"/>
       <c r="AU34" s="15"/>
@@ -11007,11 +11193,11 @@
         <v>60</v>
       </c>
       <c r="Z35" s="4">
-        <f t="shared" ref="Z35:Z36" si="10">Y35*1.5</f>
+        <f t="shared" ref="Z35:Z36" si="12">Y35*1.5</f>
         <v>90</v>
       </c>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="15"/>
       <c r="AC35" s="15">
         <f t="shared" si="5"/>
         <v>22.30720412011598</v>
@@ -11055,8 +11241,14 @@
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="AQ35" s="15"/>
-      <c r="AR35" s="15"/>
+      <c r="AQ35" s="15">
+        <f t="shared" si="7"/>
+        <v>9.8638000000000012</v>
+      </c>
+      <c r="AR35" s="15">
+        <f t="shared" si="8"/>
+        <v>26.817399999999999</v>
+      </c>
       <c r="AS35" s="15"/>
       <c r="AT35" s="15"/>
       <c r="AU35" s="15"/>
@@ -11126,11 +11318,11 @@
         <v>400</v>
       </c>
       <c r="Z36" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>600</v>
       </c>
-      <c r="AA36" s="25"/>
-      <c r="AB36" s="25"/>
+      <c r="AA36" s="15"/>
+      <c r="AB36" s="15"/>
       <c r="AC36" s="15">
         <f t="shared" si="5"/>
         <v>26.378404017857147</v>
@@ -11176,8 +11368,14 @@
         <f t="shared" si="6"/>
         <v>240</v>
       </c>
-      <c r="AQ36" s="15"/>
-      <c r="AR36" s="15"/>
+      <c r="AQ36" s="15">
+        <f t="shared" si="7"/>
+        <v>35.839999999999996</v>
+      </c>
+      <c r="AR36" s="15">
+        <f t="shared" si="8"/>
+        <v>5.120000000000001</v>
+      </c>
       <c r="AS36" s="15"/>
       <c r="AT36" s="15"/>
       <c r="AU36" s="15"/>
@@ -11243,11 +11441,11 @@
       </c>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA37" s="25"/>
-      <c r="AB37" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
       <c r="AC37" s="15">
         <f t="shared" si="5"/>
         <v>16.798543046357619</v>
@@ -11291,8 +11489,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ37" s="15"/>
-      <c r="AR37" s="15"/>
+      <c r="AQ37" s="15">
+        <f t="shared" si="7"/>
+        <v>27.18</v>
+      </c>
+      <c r="AR37" s="15">
+        <f t="shared" si="8"/>
+        <v>38.430000000000007</v>
+      </c>
       <c r="AS37" s="15"/>
       <c r="AT37" s="15"/>
       <c r="AU37" s="15"/>
@@ -11334,7 +11538,7 @@
         <v>444</v>
       </c>
       <c r="L38" s="15">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
         <v>-162</v>
       </c>
       <c r="M38" s="15"/>
@@ -11353,24 +11557,24 @@
       <c r="V38" s="15"/>
       <c r="W38" s="15"/>
       <c r="X38" s="15">
-        <f t="shared" ref="X38:X69" si="12">E38/5</f>
+        <f t="shared" ref="X38:X69" si="14">E38/5</f>
         <v>56.4</v>
       </c>
       <c r="Y38" s="4">
         <v>100</v>
       </c>
       <c r="Z38" s="4">
-        <f t="shared" ref="Z38:Z40" si="13">Y38*1.5</f>
+        <f t="shared" ref="Z38:Z40" si="15">Y38*1.5</f>
         <v>150</v>
       </c>
-      <c r="AA38" s="25"/>
-      <c r="AB38" s="25"/>
+      <c r="AA38" s="15"/>
+      <c r="AB38" s="15"/>
       <c r="AC38" s="15">
         <f t="shared" si="5"/>
         <v>16.556737588652485</v>
       </c>
       <c r="AD38" s="15">
-        <f t="shared" ref="AD38:AD69" si="14">(F38+O38+P38+R38+S38+T38+U38+V38+W38)/X38</f>
+        <f t="shared" ref="AD38:AD69" si="16">(F38+O38+P38+R38+S38+T38+U38+V38+W38)/X38</f>
         <v>13.897163120567379</v>
       </c>
       <c r="AE38" s="15">
@@ -11408,8 +11612,14 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="AQ38" s="15"/>
-      <c r="AR38" s="15"/>
+      <c r="AQ38" s="15">
+        <f t="shared" si="7"/>
+        <v>22.560000000000002</v>
+      </c>
+      <c r="AR38" s="15">
+        <f t="shared" si="8"/>
+        <v>28.960000000000004</v>
+      </c>
       <c r="AS38" s="15"/>
       <c r="AT38" s="15"/>
       <c r="AU38" s="15"/>
@@ -11449,7 +11659,7 @@
         <v>135</v>
       </c>
       <c r="L39" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-136</v>
       </c>
       <c r="M39" s="15"/>
@@ -11472,24 +11682,24 @@
       </c>
       <c r="W39" s="15"/>
       <c r="X39" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
       <c r="Y39" s="4">
         <v>100</v>
       </c>
       <c r="Z39" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>150</v>
       </c>
-      <c r="AA39" s="25"/>
-      <c r="AB39" s="25"/>
+      <c r="AA39" s="15"/>
+      <c r="AB39" s="15"/>
       <c r="AC39" s="15">
         <f t="shared" si="5"/>
         <v>-740</v>
       </c>
       <c r="AD39" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="AE39" s="15">
@@ -11527,8 +11737,14 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="AQ39" s="15"/>
-      <c r="AR39" s="15"/>
+      <c r="AQ39" s="15">
+        <f t="shared" si="7"/>
+        <v>-8.0000000000000016E-2</v>
+      </c>
+      <c r="AR39" s="15">
+        <f t="shared" si="8"/>
+        <v>-8.0000000000000016E-2</v>
+      </c>
       <c r="AS39" s="15"/>
       <c r="AT39" s="15"/>
       <c r="AU39" s="15"/>
@@ -11570,7 +11786,7 @@
         <v>65.5</v>
       </c>
       <c r="L40" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-0.52599999999999625</v>
       </c>
       <c r="M40" s="15"/>
@@ -11589,7 +11805,7 @@
       <c r="V40" s="15"/>
       <c r="W40" s="15"/>
       <c r="X40" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>12.994800000000001</v>
       </c>
       <c r="Y40" s="4">
@@ -11597,17 +11813,17 @@
         <v>9.6718000000000046</v>
       </c>
       <c r="Z40" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>14.507700000000007</v>
       </c>
-      <c r="AA40" s="25"/>
-      <c r="AB40" s="25"/>
+      <c r="AA40" s="15"/>
+      <c r="AB40" s="15"/>
       <c r="AC40" s="15">
         <f t="shared" si="5"/>
         <v>11.37214116415797</v>
       </c>
       <c r="AD40" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>10.255717671684058</v>
       </c>
       <c r="AE40" s="15">
@@ -11647,8 +11863,14 @@
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="AQ40" s="15"/>
-      <c r="AR40" s="15"/>
+      <c r="AQ40" s="15">
+        <f t="shared" si="7"/>
+        <v>12.994800000000001</v>
+      </c>
+      <c r="AR40" s="15">
+        <f t="shared" si="8"/>
+        <v>12.9156</v>
+      </c>
       <c r="AS40" s="15"/>
       <c r="AT40" s="15"/>
       <c r="AU40" s="15"/>
@@ -11690,7 +11912,7 @@
         <v>230</v>
       </c>
       <c r="L41" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-14</v>
       </c>
       <c r="M41" s="15"/>
@@ -11709,19 +11931,19 @@
       <c r="V41" s="15"/>
       <c r="W41" s="15"/>
       <c r="X41" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>43.2</v>
       </c>
       <c r="Y41" s="4"/>
       <c r="Z41" s="4">
-        <f t="shared" ref="Z41:Z43" si="15">AA41</f>
+        <f t="shared" ref="Z41:Z43" si="17">AA41</f>
         <v>200</v>
       </c>
-      <c r="AA41" s="25">
+      <c r="AA41" s="15">
         <f>VLOOKUP(A41,[1]Sheet!$A:$AA,26,0)</f>
         <v>200</v>
       </c>
-      <c r="AB41" s="25" t="str">
+      <c r="AB41" s="15" t="str">
         <f>VLOOKUP(A41,[1]Sheet!$A:$AA,27,0)</f>
         <v>Промо и сроки хорошие</v>
       </c>
@@ -11730,7 +11952,7 @@
         <v>17.944444444444443</v>
       </c>
       <c r="AD41" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>13.314814814814815</v>
       </c>
       <c r="AE41" s="15">
@@ -11770,8 +11992,14 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="AQ41" s="15"/>
-      <c r="AR41" s="15"/>
+      <c r="AQ41" s="15">
+        <f t="shared" si="7"/>
+        <v>4.32</v>
+      </c>
+      <c r="AR41" s="15">
+        <f t="shared" si="8"/>
+        <v>5.0200000000000005</v>
+      </c>
       <c r="AS41" s="15"/>
       <c r="AT41" s="15"/>
       <c r="AU41" s="15"/>
@@ -11811,7 +12039,7 @@
         <v>49</v>
       </c>
       <c r="L42" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-15</v>
       </c>
       <c r="M42" s="15"/>
@@ -11830,21 +12058,21 @@
       <c r="V42" s="15"/>
       <c r="W42" s="15"/>
       <c r="X42" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6.8</v>
       </c>
       <c r="Y42" s="4">
         <v>20</v>
       </c>
       <c r="Z42" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>130</v>
       </c>
-      <c r="AA42" s="25">
+      <c r="AA42" s="15">
         <f>VLOOKUP(A42,[1]Sheet!$A:$AA,26,0)</f>
         <v>130</v>
       </c>
-      <c r="AB42" s="25" t="str">
+      <c r="AB42" s="15" t="str">
         <f>VLOOKUP(A42,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -11853,7 +12081,7 @@
         <v>30.441176470588236</v>
       </c>
       <c r="AD42" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>11.323529411764707</v>
       </c>
       <c r="AE42" s="15">
@@ -11891,8 +12119,14 @@
         <f t="shared" si="6"/>
         <v>46</v>
       </c>
-      <c r="AQ42" s="15"/>
-      <c r="AR42" s="15"/>
+      <c r="AQ42" s="15">
+        <f t="shared" si="7"/>
+        <v>2.38</v>
+      </c>
+      <c r="AR42" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AS42" s="15"/>
       <c r="AT42" s="15"/>
       <c r="AU42" s="15"/>
@@ -11934,7 +12168,7 @@
         <v>85.1</v>
       </c>
       <c r="L43" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-39.885999999999996</v>
       </c>
       <c r="M43" s="15"/>
@@ -11953,21 +12187,21 @@
       <c r="V43" s="15"/>
       <c r="W43" s="15"/>
       <c r="X43" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>9.0427999999999997</v>
       </c>
       <c r="Y43" s="4">
         <v>10</v>
       </c>
       <c r="Z43" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>50</v>
       </c>
-      <c r="AA43" s="25">
+      <c r="AA43" s="15">
         <f>VLOOKUP(A43,[1]Sheet!$A:$AA,26,0)</f>
         <v>50</v>
       </c>
-      <c r="AB43" s="25" t="str">
+      <c r="AB43" s="15" t="str">
         <f>VLOOKUP(A43,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -11976,7 +12210,7 @@
         <v>19.914185871632679</v>
       </c>
       <c r="AD43" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>14.384925023222895</v>
       </c>
       <c r="AE43" s="15">
@@ -12016,8 +12250,14 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="AQ43" s="15"/>
-      <c r="AR43" s="15"/>
+      <c r="AQ43" s="15">
+        <f t="shared" si="7"/>
+        <v>9.0427999999999997</v>
+      </c>
+      <c r="AR43" s="15">
+        <f t="shared" si="8"/>
+        <v>8.4745999999999988</v>
+      </c>
       <c r="AS43" s="15"/>
       <c r="AT43" s="15"/>
       <c r="AU43" s="15"/>
@@ -12055,7 +12295,7 @@
         <v>10</v>
       </c>
       <c r="L44" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-10</v>
       </c>
       <c r="M44" s="11"/>
@@ -12074,22 +12314,22 @@
       <c r="V44" s="11"/>
       <c r="W44" s="11"/>
       <c r="X44" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y44" s="13"/>
       <c r="Z44" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA44" s="25"/>
-      <c r="AB44" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA44" s="15"/>
+      <c r="AB44" s="15"/>
       <c r="AC44" s="15" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD44" s="11" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE44" s="11">
@@ -12127,8 +12367,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ44" s="15"/>
-      <c r="AR44" s="15"/>
+      <c r="AQ44" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR44" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AS44" s="15"/>
       <c r="AT44" s="15"/>
       <c r="AU44" s="15"/>
@@ -12170,7 +12416,7 @@
         <v>330</v>
       </c>
       <c r="L45" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-300</v>
       </c>
       <c r="M45" s="15"/>
@@ -12189,7 +12435,7 @@
       <c r="V45" s="15"/>
       <c r="W45" s="15"/>
       <c r="X45" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="Y45" s="4"/>
@@ -12197,14 +12443,14 @@
         <f>Y45*1.5</f>
         <v>0</v>
       </c>
-      <c r="AA45" s="25"/>
-      <c r="AB45" s="25"/>
+      <c r="AA45" s="15"/>
+      <c r="AB45" s="15"/>
       <c r="AC45" s="15">
         <f t="shared" si="5"/>
         <v>50.566666666666663</v>
       </c>
       <c r="AD45" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>50.566666666666663</v>
       </c>
       <c r="AE45" s="15">
@@ -12242,8 +12488,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ45" s="15"/>
-      <c r="AR45" s="15"/>
+      <c r="AQ45" s="15">
+        <f t="shared" si="7"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="AR45" s="15">
+        <f t="shared" si="8"/>
+        <v>5.120000000000001</v>
+      </c>
       <c r="AS45" s="15"/>
       <c r="AT45" s="15"/>
       <c r="AU45" s="15"/>
@@ -12285,7 +12537,7 @@
         <v>359</v>
       </c>
       <c r="L46" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-220</v>
       </c>
       <c r="M46" s="15"/>
@@ -12304,22 +12556,22 @@
       <c r="V46" s="15"/>
       <c r="W46" s="15"/>
       <c r="X46" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>27.8</v>
       </c>
       <c r="Y46" s="4"/>
       <c r="Z46" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA46" s="25"/>
-      <c r="AB46" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="15"/>
+      <c r="AB46" s="15"/>
       <c r="AC46" s="15">
         <f t="shared" si="5"/>
         <v>14.848920863309353</v>
       </c>
       <c r="AD46" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>14.848920863309353</v>
       </c>
       <c r="AE46" s="15">
@@ -12357,8 +12609,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ46" s="15"/>
-      <c r="AR46" s="15"/>
+      <c r="AQ46" s="15">
+        <f t="shared" si="7"/>
+        <v>11.120000000000001</v>
+      </c>
+      <c r="AR46" s="15">
+        <f t="shared" si="8"/>
+        <v>14.56</v>
+      </c>
       <c r="AS46" s="15"/>
       <c r="AT46" s="15"/>
       <c r="AU46" s="15"/>
@@ -12400,7 +12658,7 @@
         <v>62.7</v>
       </c>
       <c r="L47" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-45.308000000000007</v>
       </c>
       <c r="M47" s="15"/>
@@ -12419,21 +12677,21 @@
       <c r="V47" s="15"/>
       <c r="W47" s="15"/>
       <c r="X47" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3.4783999999999997</v>
       </c>
       <c r="Y47" s="4">
         <v>50</v>
       </c>
       <c r="Z47" s="4">
-        <f t="shared" ref="Z47:Z48" si="16">AA47</f>
+        <f t="shared" ref="Z47:Z48" si="18">AA47</f>
         <v>100</v>
       </c>
-      <c r="AA47" s="25">
+      <c r="AA47" s="15">
         <f>VLOOKUP(A47,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB47" s="25" t="str">
+      <c r="AB47" s="15" t="str">
         <f>VLOOKUP(A47,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -12442,7 +12700,7 @@
         <v>63.050885464581427</v>
       </c>
       <c r="AD47" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>34.302035418583259</v>
       </c>
       <c r="AE47" s="15">
@@ -12482,8 +12740,14 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AQ47" s="15"/>
-      <c r="AR47" s="15"/>
+      <c r="AQ47" s="15">
+        <f t="shared" si="7"/>
+        <v>3.4783999999999997</v>
+      </c>
+      <c r="AR47" s="15">
+        <f t="shared" si="8"/>
+        <v>2.7585999999999999</v>
+      </c>
       <c r="AS47" s="15"/>
       <c r="AT47" s="15"/>
       <c r="AU47" s="15"/>
@@ -12525,7 +12789,7 @@
         <v>180</v>
       </c>
       <c r="L48" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-36</v>
       </c>
       <c r="M48" s="15"/>
@@ -12546,21 +12810,21 @@
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>28.8</v>
       </c>
       <c r="Y48" s="4">
         <v>200</v>
       </c>
       <c r="Z48" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>300</v>
       </c>
-      <c r="AA48" s="25">
+      <c r="AA48" s="15">
         <f>VLOOKUP(A48,[1]Sheet!$A:$AA,26,0)</f>
         <v>300</v>
       </c>
-      <c r="AB48" s="25" t="str">
+      <c r="AB48" s="15" t="str">
         <f>VLOOKUP(A48,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -12569,7 +12833,7 @@
         <v>15.305555555555552</v>
       </c>
       <c r="AD48" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4.8888888888888848</v>
       </c>
       <c r="AE48" s="15">
@@ -12607,8 +12871,14 @@
         <f t="shared" si="6"/>
         <v>105</v>
       </c>
-      <c r="AQ48" s="15"/>
-      <c r="AR48" s="15"/>
+      <c r="AQ48" s="15">
+        <f t="shared" si="7"/>
+        <v>10.08</v>
+      </c>
+      <c r="AR48" s="15">
+        <f t="shared" si="8"/>
+        <v>12.389999999999999</v>
+      </c>
       <c r="AS48" s="15"/>
       <c r="AT48" s="15"/>
       <c r="AU48" s="15"/>
@@ -12650,7 +12920,7 @@
         <v>368</v>
       </c>
       <c r="L49" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-124</v>
       </c>
       <c r="M49" s="15"/>
@@ -12669,7 +12939,7 @@
       <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>48.8</v>
       </c>
       <c r="Y49" s="4"/>
@@ -12677,14 +12947,14 @@
         <f>Y49*1.5</f>
         <v>0</v>
       </c>
-      <c r="AA49" s="25"/>
-      <c r="AB49" s="25"/>
+      <c r="AA49" s="15"/>
+      <c r="AB49" s="15"/>
       <c r="AC49" s="15">
         <f t="shared" si="5"/>
         <v>21.639344262295083</v>
       </c>
       <c r="AD49" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>21.639344262295083</v>
       </c>
       <c r="AE49" s="15">
@@ -12722,8 +12992,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ49" s="15"/>
-      <c r="AR49" s="15"/>
+      <c r="AQ49" s="15">
+        <f t="shared" si="7"/>
+        <v>19.52</v>
+      </c>
+      <c r="AR49" s="15">
+        <f t="shared" si="8"/>
+        <v>39.200000000000003</v>
+      </c>
       <c r="AS49" s="15"/>
       <c r="AT49" s="15"/>
       <c r="AU49" s="15"/>
@@ -12765,7 +13041,7 @@
         <v>65.5</v>
       </c>
       <c r="L50" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-0.60500000000000398</v>
       </c>
       <c r="M50" s="15"/>
@@ -12784,22 +13060,22 @@
       <c r="V50" s="15"/>
       <c r="W50" s="15"/>
       <c r="X50" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>12.978999999999999</v>
       </c>
       <c r="Y50" s="4"/>
       <c r="Z50" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA50" s="25"/>
-      <c r="AB50" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA50" s="15"/>
+      <c r="AB50" s="15"/>
       <c r="AC50" s="15">
         <f t="shared" si="5"/>
         <v>11.110291393789971</v>
       </c>
       <c r="AD50" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>11.110291393789971</v>
       </c>
       <c r="AE50" s="15">
@@ -12837,8 +13113,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ50" s="15"/>
-      <c r="AR50" s="15"/>
+      <c r="AQ50" s="15">
+        <f t="shared" si="7"/>
+        <v>12.978999999999999</v>
+      </c>
+      <c r="AR50" s="15">
+        <f t="shared" si="8"/>
+        <v>13.252599999999999</v>
+      </c>
       <c r="AS50" s="15"/>
       <c r="AT50" s="15"/>
       <c r="AU50" s="15"/>
@@ -12880,7 +13162,7 @@
         <v>172.4</v>
       </c>
       <c r="L51" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-17.024000000000001</v>
       </c>
       <c r="M51" s="15"/>
@@ -12899,7 +13181,7 @@
       <c r="V51" s="15"/>
       <c r="W51" s="15"/>
       <c r="X51" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>31.075200000000002</v>
       </c>
       <c r="Y51" s="4">
@@ -12910,14 +13192,14 @@
         <f>Y51+X51*$Z$1</f>
         <v>119.06156000000001</v>
       </c>
-      <c r="AA51" s="25"/>
-      <c r="AB51" s="25"/>
+      <c r="AA51" s="15"/>
+      <c r="AB51" s="15"/>
       <c r="AC51" s="15">
         <f t="shared" si="5"/>
         <v>12.799999999999999</v>
       </c>
       <c r="AD51" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>8.9685987539903209</v>
       </c>
       <c r="AE51" s="15">
@@ -12957,8 +13239,14 @@
         <f t="shared" si="6"/>
         <v>119</v>
       </c>
-      <c r="AQ51" s="15"/>
-      <c r="AR51" s="15"/>
+      <c r="AQ51" s="15">
+        <f t="shared" si="7"/>
+        <v>31.075200000000002</v>
+      </c>
+      <c r="AR51" s="15">
+        <f t="shared" si="8"/>
+        <v>26.267199999999999</v>
+      </c>
       <c r="AS51" s="15"/>
       <c r="AT51" s="15"/>
       <c r="AU51" s="15"/>
@@ -12996,7 +13284,7 @@
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
       <c r="L52" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-5.1449999999999996</v>
       </c>
       <c r="M52" s="15"/>
@@ -13019,7 +13307,7 @@
       </c>
       <c r="W52" s="15"/>
       <c r="X52" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-1.0289999999999999</v>
       </c>
       <c r="Y52" s="4">
@@ -13029,14 +13317,14 @@
         <f>Y52*1.5</f>
         <v>150</v>
       </c>
-      <c r="AA52" s="25"/>
-      <c r="AB52" s="25"/>
+      <c r="AA52" s="15"/>
+      <c r="AB52" s="15"/>
       <c r="AC52" s="15">
         <f t="shared" si="5"/>
         <v>-137.44800777453838</v>
       </c>
       <c r="AD52" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>8.324586977648206</v>
       </c>
       <c r="AE52" s="15">
@@ -13074,8 +13362,14 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AQ52" s="15"/>
-      <c r="AR52" s="15"/>
+      <c r="AQ52" s="15">
+        <f t="shared" si="7"/>
+        <v>-1.0289999999999999</v>
+      </c>
+      <c r="AR52" s="15">
+        <f t="shared" si="8"/>
+        <v>-0.15640000000000001</v>
+      </c>
       <c r="AS52" s="15"/>
       <c r="AT52" s="15"/>
       <c r="AU52" s="15"/>
@@ -13117,7 +13411,7 @@
         <v>163</v>
       </c>
       <c r="L53" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-15</v>
       </c>
       <c r="M53" s="15"/>
@@ -13136,7 +13430,7 @@
       <c r="V53" s="15"/>
       <c r="W53" s="15"/>
       <c r="X53" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>29.6</v>
       </c>
       <c r="Y53" s="4"/>
@@ -13144,11 +13438,11 @@
         <f>AA53</f>
         <v>100</v>
       </c>
-      <c r="AA53" s="25">
+      <c r="AA53" s="15">
         <f>VLOOKUP(A53,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB53" s="25" t="str">
+      <c r="AB53" s="15" t="str">
         <f>VLOOKUP(A53,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -13157,7 +13451,7 @@
         <v>20.472972972972972</v>
       </c>
       <c r="AD53" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>17.094594594594593</v>
       </c>
       <c r="AE53" s="15">
@@ -13195,8 +13489,14 @@
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="AQ53" s="15"/>
-      <c r="AR53" s="15"/>
+      <c r="AQ53" s="15">
+        <f t="shared" si="7"/>
+        <v>13.32</v>
+      </c>
+      <c r="AR53" s="15">
+        <f t="shared" si="8"/>
+        <v>19.350000000000001</v>
+      </c>
       <c r="AS53" s="15"/>
       <c r="AT53" s="15"/>
       <c r="AU53" s="15"/>
@@ -13238,7 +13538,7 @@
         <v>78</v>
       </c>
       <c r="L54" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M54" s="15"/>
@@ -13257,22 +13557,22 @@
       <c r="V54" s="15"/>
       <c r="W54" s="15"/>
       <c r="X54" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>15.8</v>
       </c>
       <c r="Y54" s="4"/>
       <c r="Z54" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA54" s="25"/>
-      <c r="AB54" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA54" s="15"/>
+      <c r="AB54" s="15"/>
       <c r="AC54" s="15">
         <f t="shared" si="5"/>
         <v>39.424556962025321</v>
       </c>
       <c r="AD54" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>39.424556962025321</v>
       </c>
       <c r="AE54" s="15">
@@ -13312,8 +13612,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ54" s="15"/>
-      <c r="AR54" s="15"/>
+      <c r="AQ54" s="15">
+        <f t="shared" si="7"/>
+        <v>7.11</v>
+      </c>
+      <c r="AR54" s="15">
+        <f t="shared" si="8"/>
+        <v>21.509999999999998</v>
+      </c>
       <c r="AS54" s="15"/>
       <c r="AT54" s="15"/>
       <c r="AU54" s="15"/>
@@ -13353,7 +13659,7 @@
         <v>41</v>
       </c>
       <c r="L55" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-42</v>
       </c>
       <c r="M55" s="15"/>
@@ -13372,24 +13678,24 @@
       <c r="V55" s="15"/>
       <c r="W55" s="15"/>
       <c r="X55" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.2</v>
       </c>
       <c r="Y55" s="4">
         <v>30</v>
       </c>
       <c r="Z55" s="4">
-        <f t="shared" ref="Z55:Z56" si="17">Y55*1.5</f>
+        <f t="shared" ref="Z55:Z56" si="19">Y55*1.5</f>
         <v>45</v>
       </c>
-      <c r="AA55" s="25"/>
-      <c r="AB55" s="25"/>
+      <c r="AA55" s="15"/>
+      <c r="AB55" s="15"/>
       <c r="AC55" s="15">
         <f t="shared" si="5"/>
         <v>-550</v>
       </c>
       <c r="AD55" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-325</v>
       </c>
       <c r="AE55" s="15">
@@ -13427,8 +13733,14 @@
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="AQ55" s="15"/>
-      <c r="AR55" s="15"/>
+      <c r="AQ55" s="15">
+        <f t="shared" si="7"/>
+        <v>-8.0000000000000016E-2</v>
+      </c>
+      <c r="AR55" s="15">
+        <f t="shared" si="8"/>
+        <v>-8.0000000000000016E-2</v>
+      </c>
       <c r="AS55" s="15"/>
       <c r="AT55" s="15"/>
       <c r="AU55" s="15"/>
@@ -13470,7 +13782,7 @@
         <v>37</v>
       </c>
       <c r="L56" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-35</v>
       </c>
       <c r="M56" s="15"/>
@@ -13489,22 +13801,22 @@
       <c r="V56" s="15"/>
       <c r="W56" s="15"/>
       <c r="X56" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.4</v>
       </c>
       <c r="Y56" s="4"/>
       <c r="Z56" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AA56" s="25"/>
-      <c r="AB56" s="25"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA56" s="15"/>
+      <c r="AB56" s="15"/>
       <c r="AC56" s="15">
         <f t="shared" si="5"/>
         <v>282.5</v>
       </c>
       <c r="AD56" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>282.5</v>
       </c>
       <c r="AE56" s="15">
@@ -13542,8 +13854,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ56" s="15"/>
-      <c r="AR56" s="15"/>
+      <c r="AQ56" s="15">
+        <f t="shared" si="7"/>
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="AR56" s="15">
+        <f t="shared" si="8"/>
+        <v>2.3199999999999998</v>
+      </c>
       <c r="AS56" s="15"/>
       <c r="AT56" s="15"/>
       <c r="AU56" s="15"/>
@@ -13585,7 +13903,7 @@
         <v>83.21</v>
       </c>
       <c r="L57" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-11.773999999999987</v>
       </c>
       <c r="M57" s="15"/>
@@ -13604,7 +13922,7 @@
       <c r="V57" s="15"/>
       <c r="W57" s="15"/>
       <c r="X57" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>14.287200000000002</v>
       </c>
       <c r="Y57" s="4"/>
@@ -13612,11 +13930,11 @@
         <f>AA57</f>
         <v>150</v>
       </c>
-      <c r="AA57" s="25">
+      <c r="AA57" s="15">
         <f>VLOOKUP(A57,[1]Sheet!$A:$AA,26,0)</f>
         <v>150</v>
       </c>
-      <c r="AB57" s="25" t="str">
+      <c r="AB57" s="15" t="str">
         <f>VLOOKUP(A57,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -13625,7 +13943,7 @@
         <v>23.088596785934261</v>
       </c>
       <c r="AD57" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>12.58968867237807</v>
       </c>
       <c r="AE57" s="15">
@@ -13665,8 +13983,14 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AQ57" s="15"/>
-      <c r="AR57" s="15"/>
+      <c r="AQ57" s="15">
+        <f t="shared" si="7"/>
+        <v>14.287200000000002</v>
+      </c>
+      <c r="AR57" s="15">
+        <f t="shared" si="8"/>
+        <v>18.321200000000001</v>
+      </c>
       <c r="AS57" s="15"/>
       <c r="AT57" s="15"/>
       <c r="AU57" s="15"/>
@@ -13710,7 +14034,7 @@
         <v>179</v>
       </c>
       <c r="L58" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>64</v>
       </c>
       <c r="M58" s="15"/>
@@ -13729,22 +14053,22 @@
       <c r="V58" s="15"/>
       <c r="W58" s="15"/>
       <c r="X58" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>48.6</v>
       </c>
       <c r="Y58" s="4"/>
       <c r="Z58" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA58" s="25"/>
-      <c r="AB58" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA58" s="15"/>
+      <c r="AB58" s="15"/>
       <c r="AC58" s="15">
         <f t="shared" si="5"/>
         <v>14.666666666666668</v>
       </c>
       <c r="AD58" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>14.666666666666668</v>
       </c>
       <c r="AE58" s="15">
@@ -13784,8 +14108,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ58" s="15"/>
-      <c r="AR58" s="15"/>
+      <c r="AQ58" s="15">
+        <f t="shared" si="7"/>
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="AR58" s="15">
+        <f t="shared" si="8"/>
+        <v>6.2600000000000007</v>
+      </c>
       <c r="AS58" s="15"/>
       <c r="AT58" s="15"/>
       <c r="AU58" s="15"/>
@@ -13827,7 +14157,7 @@
         <v>152.19999999999999</v>
       </c>
       <c r="L59" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-8.8799999999999955</v>
       </c>
       <c r="M59" s="15"/>
@@ -13846,7 +14176,7 @@
       <c r="V59" s="15"/>
       <c r="W59" s="15"/>
       <c r="X59" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>28.663999999999998</v>
       </c>
       <c r="Y59" s="4">
@@ -13857,14 +14187,14 @@
         <f>Y59+X59*$Z$1</f>
         <v>142.58859999999996</v>
       </c>
-      <c r="AA59" s="25"/>
-      <c r="AB59" s="25"/>
+      <c r="AA59" s="15"/>
+      <c r="AB59" s="15"/>
       <c r="AC59" s="15">
         <f t="shared" si="5"/>
         <v>12.799999999999999</v>
       </c>
       <c r="AD59" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>7.8255163271001953</v>
       </c>
       <c r="AE59" s="15">
@@ -13904,8 +14234,14 @@
         <f t="shared" si="6"/>
         <v>143</v>
       </c>
-      <c r="AQ59" s="15"/>
-      <c r="AR59" s="15"/>
+      <c r="AQ59" s="15">
+        <f t="shared" si="7"/>
+        <v>28.663999999999998</v>
+      </c>
+      <c r="AR59" s="15">
+        <f t="shared" si="8"/>
+        <v>22.774799999999999</v>
+      </c>
       <c r="AS59" s="15"/>
       <c r="AT59" s="15"/>
       <c r="AU59" s="15"/>
@@ -13947,7 +14283,7 @@
         <v>32.9</v>
       </c>
       <c r="L60" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-0.13499999999999801</v>
       </c>
       <c r="M60" s="15"/>
@@ -13966,22 +14302,22 @@
       <c r="V60" s="15"/>
       <c r="W60" s="15"/>
       <c r="X60" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6.5529999999999999</v>
       </c>
       <c r="Y60" s="4"/>
       <c r="Z60" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA60" s="25"/>
-      <c r="AB60" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA60" s="15"/>
+      <c r="AB60" s="15"/>
       <c r="AC60" s="15">
         <f t="shared" si="5"/>
         <v>14.727300473065773</v>
       </c>
       <c r="AD60" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>14.727300473065773</v>
       </c>
       <c r="AE60" s="15">
@@ -14019,8 +14355,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ60" s="15"/>
-      <c r="AR60" s="15"/>
+      <c r="AQ60" s="15">
+        <f t="shared" si="7"/>
+        <v>6.5529999999999999</v>
+      </c>
+      <c r="AR60" s="15">
+        <f t="shared" si="8"/>
+        <v>8.4641999999999999</v>
+      </c>
       <c r="AS60" s="15"/>
       <c r="AT60" s="15"/>
       <c r="AU60" s="15"/>
@@ -14062,7 +14404,7 @@
         <v>181</v>
       </c>
       <c r="L61" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-11</v>
       </c>
       <c r="M61" s="15"/>
@@ -14081,22 +14423,22 @@
       <c r="V61" s="15"/>
       <c r="W61" s="15"/>
       <c r="X61" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>34</v>
       </c>
       <c r="Y61" s="4"/>
       <c r="Z61" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA61" s="25"/>
-      <c r="AB61" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="15"/>
+      <c r="AB61" s="15"/>
       <c r="AC61" s="15">
         <f t="shared" si="5"/>
         <v>18.411764705882351</v>
       </c>
       <c r="AD61" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>18.411764705882351</v>
       </c>
       <c r="AE61" s="15">
@@ -14136,8 +14478,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ61" s="15"/>
-      <c r="AR61" s="15"/>
+      <c r="AQ61" s="15">
+        <f t="shared" si="7"/>
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="AR61" s="15">
+        <f t="shared" si="8"/>
+        <v>3.9600000000000004</v>
+      </c>
       <c r="AS61" s="15"/>
       <c r="AT61" s="15"/>
       <c r="AU61" s="15"/>
@@ -14179,7 +14527,7 @@
         <v>20</v>
       </c>
       <c r="L62" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M62" s="15"/>
@@ -14198,7 +14546,7 @@
       <c r="V62" s="15"/>
       <c r="W62" s="15"/>
       <c r="X62" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="Y62" s="4">
@@ -14206,17 +14554,17 @@
         <v>17.2</v>
       </c>
       <c r="Z62" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>17.2</v>
       </c>
-      <c r="AA62" s="25"/>
-      <c r="AB62" s="25"/>
+      <c r="AA62" s="15"/>
+      <c r="AB62" s="15"/>
       <c r="AC62" s="15">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AD62" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>6.6999999999999993</v>
       </c>
       <c r="AE62" s="15">
@@ -14254,8 +14602,14 @@
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="AQ62" s="15"/>
-      <c r="AR62" s="15"/>
+      <c r="AQ62" s="15">
+        <f t="shared" si="7"/>
+        <v>1.6</v>
+      </c>
+      <c r="AR62" s="15">
+        <f t="shared" si="8"/>
+        <v>1.36</v>
+      </c>
       <c r="AS62" s="15"/>
       <c r="AT62" s="15"/>
       <c r="AU62" s="15"/>
@@ -14297,7 +14651,7 @@
         <v>201.7</v>
       </c>
       <c r="L63" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-93.724999999999994</v>
       </c>
       <c r="M63" s="15"/>
@@ -14316,22 +14670,22 @@
       <c r="V63" s="15"/>
       <c r="W63" s="15"/>
       <c r="X63" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>21.594999999999999</v>
       </c>
       <c r="Y63" s="4"/>
       <c r="Z63" s="4">
-        <f t="shared" ref="Z63:Z65" si="18">Y63*1.5</f>
-        <v>0</v>
-      </c>
-      <c r="AA63" s="25"/>
-      <c r="AB63" s="25"/>
+        <f t="shared" ref="Z63:Z65" si="20">Y63*1.5</f>
+        <v>0</v>
+      </c>
+      <c r="AA63" s="15"/>
+      <c r="AB63" s="15"/>
       <c r="AC63" s="15">
         <f t="shared" si="5"/>
         <v>12.41301227135911</v>
       </c>
       <c r="AD63" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>12.41301227135911</v>
       </c>
       <c r="AE63" s="15">
@@ -14369,8 +14723,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="15"/>
-      <c r="AR63" s="15"/>
+      <c r="AQ63" s="15">
+        <f t="shared" si="7"/>
+        <v>21.594999999999999</v>
+      </c>
+      <c r="AR63" s="15">
+        <f t="shared" si="8"/>
+        <v>26.615600000000001</v>
+      </c>
       <c r="AS63" s="15"/>
       <c r="AT63" s="15"/>
       <c r="AU63" s="15"/>
@@ -14412,7 +14772,7 @@
         <v>201.8</v>
       </c>
       <c r="L64" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-6.65300000000002</v>
       </c>
       <c r="M64" s="15"/>
@@ -14433,24 +14793,24 @@
       </c>
       <c r="W64" s="15"/>
       <c r="X64" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>39.029399999999995</v>
       </c>
       <c r="Y64" s="4">
         <v>100</v>
       </c>
       <c r="Z64" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>150</v>
       </c>
-      <c r="AA64" s="25"/>
-      <c r="AB64" s="25"/>
+      <c r="AA64" s="15"/>
+      <c r="AB64" s="15"/>
       <c r="AC64" s="15">
         <f t="shared" si="5"/>
         <v>4.9429404500197291</v>
       </c>
       <c r="AD64" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.099683828088569</v>
       </c>
       <c r="AE64" s="15">
@@ -14488,8 +14848,14 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AQ64" s="15"/>
-      <c r="AR64" s="15"/>
+      <c r="AQ64" s="15">
+        <f t="shared" si="7"/>
+        <v>39.029399999999995</v>
+      </c>
+      <c r="AR64" s="15">
+        <f t="shared" si="8"/>
+        <v>33.448999999999998</v>
+      </c>
       <c r="AS64" s="15"/>
       <c r="AT64" s="15"/>
       <c r="AU64" s="15"/>
@@ -14531,7 +14897,7 @@
         <v>488</v>
       </c>
       <c r="L65" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-344</v>
       </c>
       <c r="M65" s="15"/>
@@ -14550,24 +14916,24 @@
       <c r="V65" s="15"/>
       <c r="W65" s="15"/>
       <c r="X65" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>28.8</v>
       </c>
       <c r="Y65" s="4">
         <v>300</v>
       </c>
       <c r="Z65" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>450</v>
       </c>
-      <c r="AA65" s="25"/>
-      <c r="AB65" s="25"/>
+      <c r="AA65" s="15"/>
+      <c r="AB65" s="15"/>
       <c r="AC65" s="15">
         <f t="shared" si="5"/>
         <v>46.770833333333336</v>
       </c>
       <c r="AD65" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>31.145833333333332</v>
       </c>
       <c r="AE65" s="15">
@@ -14605,8 +14971,14 @@
         <f t="shared" si="6"/>
         <v>180</v>
       </c>
-      <c r="AQ65" s="15"/>
-      <c r="AR65" s="15"/>
+      <c r="AQ65" s="15">
+        <f t="shared" si="7"/>
+        <v>11.520000000000001</v>
+      </c>
+      <c r="AR65" s="15">
+        <f t="shared" si="8"/>
+        <v>3.6</v>
+      </c>
       <c r="AS65" s="15"/>
       <c r="AT65" s="15"/>
       <c r="AU65" s="15"/>
@@ -14648,7 +15020,7 @@
         <v>312</v>
       </c>
       <c r="L66" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-121</v>
       </c>
       <c r="M66" s="15"/>
@@ -14667,22 +15039,22 @@
       <c r="V66" s="15"/>
       <c r="W66" s="15"/>
       <c r="X66" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>38.200000000000003</v>
       </c>
       <c r="Y66" s="4"/>
       <c r="Z66" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA66" s="25"/>
-      <c r="AB66" s="25"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA66" s="15"/>
+      <c r="AB66" s="15"/>
       <c r="AC66" s="15">
         <f t="shared" si="5"/>
         <v>15.890052356020941</v>
       </c>
       <c r="AD66" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>15.890052356020941</v>
       </c>
       <c r="AE66" s="15">
@@ -14720,8 +15092,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ66" s="15"/>
-      <c r="AR66" s="15"/>
+      <c r="AQ66" s="15">
+        <f t="shared" si="7"/>
+        <v>15.280000000000001</v>
+      </c>
+      <c r="AR66" s="15">
+        <f t="shared" si="8"/>
+        <v>21.6</v>
+      </c>
       <c r="AS66" s="15"/>
       <c r="AT66" s="15"/>
       <c r="AU66" s="15"/>
@@ -14763,7 +15141,7 @@
         <v>72.8</v>
       </c>
       <c r="L67" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-31.915999999999997</v>
       </c>
       <c r="M67" s="15"/>
@@ -14784,7 +15162,7 @@
       </c>
       <c r="W67" s="15"/>
       <c r="X67" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>8.1768000000000001</v>
       </c>
       <c r="Y67" s="4">
@@ -14794,14 +15172,14 @@
         <f>Y67*1.5</f>
         <v>75</v>
       </c>
-      <c r="AA67" s="25"/>
-      <c r="AB67" s="25"/>
+      <c r="AA67" s="15"/>
+      <c r="AB67" s="15"/>
       <c r="AC67" s="15">
         <f t="shared" si="5"/>
         <v>22.556745915272479</v>
       </c>
       <c r="AD67" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>13.384453575971039</v>
       </c>
       <c r="AE67" s="15">
@@ -14839,8 +15217,14 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="AQ67" s="15"/>
-      <c r="AR67" s="15"/>
+      <c r="AQ67" s="15">
+        <f t="shared" si="7"/>
+        <v>8.1768000000000001</v>
+      </c>
+      <c r="AR67" s="15">
+        <f t="shared" si="8"/>
+        <v>2.9136000000000002</v>
+      </c>
       <c r="AS67" s="15"/>
       <c r="AT67" s="15"/>
       <c r="AU67" s="15"/>
@@ -14882,7 +15266,7 @@
         <v>98.5</v>
       </c>
       <c r="L68" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-104.851</v>
       </c>
       <c r="M68" s="15"/>
@@ -14905,7 +15289,7 @@
       </c>
       <c r="W68" s="15"/>
       <c r="X68" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-1.2702</v>
       </c>
       <c r="Y68" s="4">
@@ -14915,11 +15299,11 @@
         <f>AA68</f>
         <v>100</v>
       </c>
-      <c r="AA68" s="25">
+      <c r="AA68" s="15">
         <f>VLOOKUP(A68,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB68" s="25" t="str">
+      <c r="AB68" s="15" t="str">
         <f>VLOOKUP(A68,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -14928,7 +15312,7 @@
         <v>-81.690284994489062</v>
       </c>
       <c r="AD68" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-2.9625255865218119</v>
       </c>
       <c r="AE68" s="15">
@@ -14966,8 +15350,14 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AQ68" s="15"/>
-      <c r="AR68" s="15"/>
+      <c r="AQ68" s="15">
+        <f t="shared" si="7"/>
+        <v>-1.2702</v>
+      </c>
+      <c r="AR68" s="15">
+        <f t="shared" si="8"/>
+        <v>-1.0875999999999999</v>
+      </c>
       <c r="AS68" s="15"/>
       <c r="AT68" s="15"/>
       <c r="AU68" s="15"/>
@@ -15009,7 +15399,7 @@
         <v>192.2</v>
       </c>
       <c r="L69" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-196.70599999999999</v>
       </c>
       <c r="M69" s="15"/>
@@ -15028,7 +15418,7 @@
       <c r="V69" s="15"/>
       <c r="W69" s="15"/>
       <c r="X69" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-0.9012</v>
       </c>
       <c r="Y69" s="4"/>
@@ -15036,14 +15426,14 @@
         <f>Y69*1.5</f>
         <v>0</v>
       </c>
-      <c r="AA69" s="25"/>
-      <c r="AB69" s="25"/>
+      <c r="AA69" s="15"/>
+      <c r="AB69" s="15"/>
       <c r="AC69" s="15">
         <f t="shared" si="5"/>
         <v>-780.96537949400806</v>
       </c>
       <c r="AD69" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-780.96537949400806</v>
       </c>
       <c r="AE69" s="15">
@@ -15081,8 +15471,14 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AQ69" s="15"/>
-      <c r="AR69" s="15"/>
+      <c r="AQ69" s="15">
+        <f t="shared" si="7"/>
+        <v>-0.9012</v>
+      </c>
+      <c r="AR69" s="15">
+        <f t="shared" si="8"/>
+        <v>26.5594</v>
+      </c>
       <c r="AS69" s="15"/>
       <c r="AT69" s="15"/>
       <c r="AU69" s="15"/>
@@ -15124,7 +15520,7 @@
         <v>174.6</v>
       </c>
       <c r="L70" s="15">
-        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
         <v>-102.80799999999999</v>
       </c>
       <c r="M70" s="15"/>
@@ -15147,7 +15543,7 @@
       </c>
       <c r="W70" s="15"/>
       <c r="X70" s="15">
-        <f t="shared" ref="X70:X101" si="20">E70/5</f>
+        <f t="shared" ref="X70:X101" si="22">E70/5</f>
         <v>14.3584</v>
       </c>
       <c r="Y70" s="4">
@@ -15157,11 +15553,11 @@
         <f>AA70</f>
         <v>100</v>
       </c>
-      <c r="AA70" s="25">
+      <c r="AA70" s="15">
         <f>VLOOKUP(A70,[1]Sheet!$A:$AA,26,0)</f>
         <v>100</v>
       </c>
-      <c r="AB70" s="25" t="str">
+      <c r="AB70" s="15" t="str">
         <f>VLOOKUP(A70,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -15170,7 +15566,7 @@
         <v>7.2861182304435044</v>
       </c>
       <c r="AD70" s="15">
-        <f t="shared" ref="AD70:AD91" si="21">(F70+O70+P70+R70+S70+T70+U70+V70+W70)/X70</f>
+        <f t="shared" ref="AD70:AD91" si="23">(F70+O70+P70+R70+S70+T70+U70+V70+W70)/X70</f>
         <v>0.32155393358591516</v>
       </c>
       <c r="AE70" s="15">
@@ -15208,8 +15604,14 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AQ70" s="15"/>
-      <c r="AR70" s="15"/>
+      <c r="AQ70" s="15">
+        <f t="shared" si="7"/>
+        <v>14.3584</v>
+      </c>
+      <c r="AR70" s="15">
+        <f t="shared" si="8"/>
+        <v>-0.11700000000000001</v>
+      </c>
       <c r="AS70" s="15"/>
       <c r="AT70" s="15"/>
       <c r="AU70" s="15"/>
@@ -15239,7 +15641,7 @@
       <c r="J71" s="11"/>
       <c r="K71" s="11"/>
       <c r="L71" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M71" s="11"/>
@@ -15258,22 +15660,22 @@
       <c r="V71" s="11"/>
       <c r="W71" s="11"/>
       <c r="X71" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y71" s="13"/>
       <c r="Z71" s="4">
-        <f t="shared" ref="Z71:Z132" si="22">Y71</f>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="25"/>
-      <c r="AB71" s="25"/>
+        <f t="shared" ref="Z71:Z132" si="24">Y71</f>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="15"/>
+      <c r="AB71" s="15"/>
       <c r="AC71" s="15" t="e">
-        <f t="shared" ref="AC71:AC132" si="23">(F71+O71+P71+Q71+R71+S71+T71+U71+V71+W71+Z71)/X71</f>
+        <f t="shared" ref="AC71:AC132" si="25">(F71+O71+P71+Q71+R71+S71+T71+U71+V71+W71+Z71)/X71</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD71" s="11" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE71" s="11">
@@ -15310,11 +15712,17 @@
         <v>48</v>
       </c>
       <c r="AP71" s="15">
-        <f t="shared" ref="AP71:AP132" si="24">ROUND(G71*Z71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ71" s="15"/>
-      <c r="AR71" s="15"/>
+        <f t="shared" ref="AP71:AP132" si="26">ROUND(G71*Z71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="15">
+        <f t="shared" ref="AQ71:AQ132" si="27">X71*G71</f>
+        <v>0</v>
+      </c>
+      <c r="AR71" s="15">
+        <f t="shared" ref="AR71:AR132" si="28">AE71*G71</f>
+        <v>0</v>
+      </c>
       <c r="AS71" s="15"/>
       <c r="AT71" s="15"/>
       <c r="AU71" s="15"/>
@@ -15356,7 +15764,7 @@
         <v>226.2</v>
       </c>
       <c r="L72" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-194.67099999999999</v>
       </c>
       <c r="M72" s="15"/>
@@ -15375,7 +15783,7 @@
       <c r="V72" s="15"/>
       <c r="W72" s="15"/>
       <c r="X72" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.3057999999999996</v>
       </c>
       <c r="Y72" s="4"/>
@@ -15383,16 +15791,16 @@
         <f>Y72*1.5</f>
         <v>0</v>
       </c>
-      <c r="AA72" s="25"/>
-      <c r="AB72" s="25"/>
+      <c r="AA72" s="15"/>
+      <c r="AB72" s="15"/>
       <c r="AC72" s="15">
+        <f t="shared" si="25"/>
+        <v>63.032922071743478</v>
+      </c>
+      <c r="AD72" s="15">
         <f t="shared" si="23"/>
         <v>63.032922071743478</v>
       </c>
-      <c r="AD72" s="15">
-        <f t="shared" si="21"/>
-        <v>63.032922071743478</v>
-      </c>
       <c r="AE72" s="15">
         <v>38.624600000000001</v>
       </c>
@@ -15427,11 +15835,17 @@
         <v>184</v>
       </c>
       <c r="AP72" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="15"/>
-      <c r="AR72" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="15">
+        <f t="shared" si="27"/>
+        <v>6.3057999999999996</v>
+      </c>
+      <c r="AR72" s="15">
+        <f t="shared" si="28"/>
+        <v>38.624600000000001</v>
+      </c>
       <c r="AS72" s="15"/>
       <c r="AT72" s="15"/>
       <c r="AU72" s="15"/>
@@ -15475,7 +15889,7 @@
         <v>60</v>
       </c>
       <c r="L73" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-54</v>
       </c>
       <c r="M73" s="15"/>
@@ -15494,24 +15908,24 @@
       <c r="V73" s="15"/>
       <c r="W73" s="15"/>
       <c r="X73" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.2</v>
       </c>
       <c r="Y73" s="4"/>
       <c r="Z73" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="25"/>
-      <c r="AB73" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA73" s="15"/>
+      <c r="AB73" s="15"/>
       <c r="AC73" s="15">
+        <f t="shared" si="25"/>
+        <v>343.33333333333337</v>
+      </c>
+      <c r="AD73" s="15">
         <f t="shared" si="23"/>
         <v>343.33333333333337</v>
       </c>
-      <c r="AD73" s="15">
-        <f t="shared" si="21"/>
-        <v>343.33333333333337</v>
-      </c>
       <c r="AE73" s="15">
         <v>3.2</v>
       </c>
@@ -15544,11 +15958,17 @@
       </c>
       <c r="AO73" s="15"/>
       <c r="AP73" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ73" s="15"/>
-      <c r="AR73" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="15">
+        <f t="shared" si="27"/>
+        <v>0.72</v>
+      </c>
+      <c r="AR73" s="15">
+        <f t="shared" si="28"/>
+        <v>1.92</v>
+      </c>
       <c r="AS73" s="15"/>
       <c r="AT73" s="15"/>
       <c r="AU73" s="15"/>
@@ -15590,7 +16010,7 @@
         <v>105</v>
       </c>
       <c r="L74" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-46</v>
       </c>
       <c r="M74" s="15"/>
@@ -15609,24 +16029,24 @@
       <c r="V74" s="15"/>
       <c r="W74" s="15"/>
       <c r="X74" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11.8</v>
       </c>
       <c r="Y74" s="4"/>
       <c r="Z74" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="25"/>
-      <c r="AB74" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA74" s="15"/>
+      <c r="AB74" s="15"/>
       <c r="AC74" s="15">
+        <f t="shared" si="25"/>
+        <v>39.237288135593218</v>
+      </c>
+      <c r="AD74" s="15">
         <f t="shared" si="23"/>
         <v>39.237288135593218</v>
       </c>
-      <c r="AD74" s="15">
-        <f t="shared" si="21"/>
-        <v>39.237288135593218</v>
-      </c>
       <c r="AE74" s="15">
         <v>25.4</v>
       </c>
@@ -15661,11 +16081,17 @@
         <v>185</v>
       </c>
       <c r="AP74" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ74" s="15"/>
-      <c r="AR74" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="15">
+        <f t="shared" si="27"/>
+        <v>7.08</v>
+      </c>
+      <c r="AR74" s="15">
+        <f t="shared" si="28"/>
+        <v>15.239999999999998</v>
+      </c>
       <c r="AS74" s="15"/>
       <c r="AT74" s="15"/>
       <c r="AU74" s="15"/>
@@ -15703,7 +16129,7 @@
         <v>3</v>
       </c>
       <c r="L75" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M75" s="11"/>
@@ -15718,24 +16144,24 @@
       <c r="V75" s="11"/>
       <c r="W75" s="11"/>
       <c r="X75" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
       <c r="Y75" s="13"/>
       <c r="Z75" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA75" s="25"/>
-      <c r="AB75" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA75" s="15"/>
+      <c r="AB75" s="15"/>
       <c r="AC75" s="15">
+        <f t="shared" si="25"/>
+        <v>-5</v>
+      </c>
+      <c r="AD75" s="11">
         <f t="shared" si="23"/>
         <v>-5</v>
       </c>
-      <c r="AD75" s="11">
-        <f t="shared" si="21"/>
-        <v>-5</v>
-      </c>
       <c r="AE75" s="11">
         <v>0</v>
       </c>
@@ -15768,11 +16194,17 @@
       </c>
       <c r="AO75" s="11"/>
       <c r="AP75" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ75" s="15"/>
-      <c r="AR75" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR75" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS75" s="15"/>
       <c r="AT75" s="15"/>
       <c r="AU75" s="15"/>
@@ -15814,7 +16246,7 @@
         <v>157</v>
       </c>
       <c r="L76" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-12</v>
       </c>
       <c r="M76" s="15"/>
@@ -15835,30 +16267,30 @@
       </c>
       <c r="W76" s="15"/>
       <c r="X76" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>29</v>
       </c>
       <c r="Y76" s="4">
         <v>60</v>
       </c>
       <c r="Z76" s="4">
-        <f t="shared" ref="Z76:Z78" si="25">AA76</f>
+        <f t="shared" ref="Z76:Z78" si="29">AA76</f>
         <v>144</v>
       </c>
-      <c r="AA76" s="25">
+      <c r="AA76" s="15">
         <f>VLOOKUP(A76,[1]Sheet!$A:$AA,26,0)</f>
         <v>144</v>
       </c>
-      <c r="AB76" s="25" t="str">
+      <c r="AB76" s="15" t="str">
         <f>VLOOKUP(A76,[1]Sheet!$A:$AA,27,0)</f>
         <v>Продукт востребован, и сроки хорошие.</v>
       </c>
       <c r="AC76" s="15">
+        <f t="shared" si="25"/>
+        <v>9.4</v>
+      </c>
+      <c r="AD76" s="15">
         <f t="shared" si="23"/>
-        <v>9.4</v>
-      </c>
-      <c r="AD76" s="15">
-        <f t="shared" si="21"/>
         <v>4.4344827586206907</v>
       </c>
       <c r="AE76" s="15">
@@ -15893,11 +16325,17 @@
       </c>
       <c r="AO76" s="15"/>
       <c r="AP76" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>58</v>
       </c>
-      <c r="AQ76" s="15"/>
-      <c r="AR76" s="15"/>
+      <c r="AQ76" s="15">
+        <f t="shared" si="27"/>
+        <v>11.600000000000001</v>
+      </c>
+      <c r="AR76" s="15">
+        <f t="shared" si="28"/>
+        <v>11.120000000000001</v>
+      </c>
       <c r="AS76" s="15"/>
       <c r="AT76" s="15"/>
       <c r="AU76" s="15"/>
@@ -15939,7 +16377,7 @@
         <v>242</v>
       </c>
       <c r="L77" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-61</v>
       </c>
       <c r="M77" s="15"/>
@@ -15960,30 +16398,30 @@
       </c>
       <c r="W77" s="15"/>
       <c r="X77" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>36.200000000000003</v>
       </c>
       <c r="Y77" s="4">
         <v>150</v>
       </c>
       <c r="Z77" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>184</v>
       </c>
-      <c r="AA77" s="25">
+      <c r="AA77" s="15">
         <f>VLOOKUP(A77,[1]Sheet!$A:$AA,26,0)</f>
         <v>184</v>
       </c>
-      <c r="AB77" s="25" t="str">
+      <c r="AB77" s="15" t="str">
         <f>VLOOKUP(A77,[1]Sheet!$A:$AA,27,0)</f>
         <v>Продукт востребован, и сроки хорошие.</v>
       </c>
       <c r="AC77" s="15">
+        <f t="shared" si="25"/>
+        <v>10.933701657458563</v>
+      </c>
+      <c r="AD77" s="15">
         <f t="shared" si="23"/>
-        <v>10.933701657458563</v>
-      </c>
-      <c r="AD77" s="15">
-        <f t="shared" si="21"/>
         <v>5.8508287292817682</v>
       </c>
       <c r="AE77" s="15">
@@ -16018,11 +16456,17 @@
       </c>
       <c r="AO77" s="15"/>
       <c r="AP77" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>61</v>
       </c>
-      <c r="AQ77" s="15"/>
-      <c r="AR77" s="15"/>
+      <c r="AQ77" s="15">
+        <f t="shared" si="27"/>
+        <v>11.946000000000002</v>
+      </c>
+      <c r="AR77" s="15">
+        <f t="shared" si="28"/>
+        <v>12.012</v>
+      </c>
       <c r="AS77" s="15"/>
       <c r="AT77" s="15"/>
       <c r="AU77" s="15"/>
@@ -16064,7 +16508,7 @@
         <v>185</v>
       </c>
       <c r="L78" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-18</v>
       </c>
       <c r="M78" s="15"/>
@@ -16085,30 +16529,30 @@
       </c>
       <c r="W78" s="15"/>
       <c r="X78" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>33.4</v>
       </c>
       <c r="Y78" s="4">
         <v>150</v>
       </c>
       <c r="Z78" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>224</v>
       </c>
-      <c r="AA78" s="25">
+      <c r="AA78" s="15">
         <f>VLOOKUP(A78,[1]Sheet!$A:$AA,26,0)</f>
         <v>224</v>
       </c>
-      <c r="AB78" s="25" t="str">
+      <c r="AB78" s="15" t="str">
         <f>VLOOKUP(A78,[1]Sheet!$A:$AA,27,0)</f>
         <v>Продукт востребован, и сроки хорошие.</v>
       </c>
       <c r="AC78" s="15">
+        <f t="shared" si="25"/>
+        <v>11.642874251497011</v>
+      </c>
+      <c r="AD78" s="15">
         <f t="shared" si="23"/>
-        <v>11.642874251497011</v>
-      </c>
-      <c r="AD78" s="15">
-        <f t="shared" si="21"/>
         <v>4.9362874251497049</v>
       </c>
       <c r="AE78" s="15">
@@ -16143,11 +16587,17 @@
       </c>
       <c r="AO78" s="15"/>
       <c r="AP78" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>78</v>
       </c>
-      <c r="AQ78" s="15"/>
-      <c r="AR78" s="15"/>
+      <c r="AQ78" s="15">
+        <f t="shared" si="27"/>
+        <v>11.69</v>
+      </c>
+      <c r="AR78" s="15">
+        <f t="shared" si="28"/>
+        <v>12.67</v>
+      </c>
       <c r="AS78" s="15"/>
       <c r="AT78" s="15"/>
       <c r="AU78" s="15"/>
@@ -16187,7 +16637,7 @@
         <v>24</v>
       </c>
       <c r="L79" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-6</v>
       </c>
       <c r="M79" s="15"/>
@@ -16206,7 +16656,7 @@
       <c r="V79" s="15"/>
       <c r="W79" s="15"/>
       <c r="X79" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3.6</v>
       </c>
       <c r="Y79" s="4">
@@ -16214,17 +16664,17 @@
         <v>20.399999999999999</v>
       </c>
       <c r="Z79" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>20.399999999999999</v>
       </c>
-      <c r="AA79" s="25"/>
-      <c r="AB79" s="25"/>
+      <c r="AA79" s="15"/>
+      <c r="AB79" s="15"/>
       <c r="AC79" s="15">
+        <f t="shared" si="25"/>
+        <v>9</v>
+      </c>
+      <c r="AD79" s="15">
         <f t="shared" si="23"/>
-        <v>9</v>
-      </c>
-      <c r="AD79" s="15">
-        <f t="shared" si="21"/>
         <v>3.333333333333333</v>
       </c>
       <c r="AE79" s="15">
@@ -16261,11 +16711,17 @@
         <v>127</v>
       </c>
       <c r="AP79" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>8</v>
       </c>
-      <c r="AQ79" s="15"/>
-      <c r="AR79" s="15"/>
+      <c r="AQ79" s="15">
+        <f t="shared" si="27"/>
+        <v>1.3320000000000001</v>
+      </c>
+      <c r="AR79" s="15">
+        <f t="shared" si="28"/>
+        <v>0.14799999999999999</v>
+      </c>
       <c r="AS79" s="15"/>
       <c r="AT79" s="15"/>
       <c r="AU79" s="15"/>
@@ -16307,7 +16763,7 @@
         <v>44</v>
       </c>
       <c r="L80" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-29</v>
       </c>
       <c r="M80" s="15"/>
@@ -16326,24 +16782,24 @@
       <c r="V80" s="15"/>
       <c r="W80" s="15"/>
       <c r="X80" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="Y80" s="4"/>
       <c r="Z80" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="25"/>
-      <c r="AB80" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA80" s="15"/>
+      <c r="AB80" s="15"/>
       <c r="AC80" s="15">
+        <f t="shared" si="25"/>
+        <v>66</v>
+      </c>
+      <c r="AD80" s="15">
         <f t="shared" si="23"/>
         <v>66</v>
       </c>
-      <c r="AD80" s="15">
-        <f t="shared" si="21"/>
-        <v>66</v>
-      </c>
       <c r="AE80" s="15">
         <v>5</v>
       </c>
@@ -16378,11 +16834,17 @@
         <v>185</v>
       </c>
       <c r="AP80" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ80" s="15"/>
-      <c r="AR80" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ80" s="15">
+        <f t="shared" si="27"/>
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="AR80" s="15">
+        <f t="shared" si="28"/>
+        <v>3</v>
+      </c>
       <c r="AS80" s="15"/>
       <c r="AT80" s="15"/>
       <c r="AU80" s="15"/>
@@ -16422,7 +16884,7 @@
         <v>84</v>
       </c>
       <c r="L81" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-5</v>
       </c>
       <c r="M81" s="15"/>
@@ -16441,7 +16903,7 @@
       <c r="V81" s="15"/>
       <c r="W81" s="15"/>
       <c r="X81" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>15.8</v>
       </c>
       <c r="Y81" s="4">
@@ -16449,17 +16911,17 @@
         <v>24.800000000000011</v>
       </c>
       <c r="Z81" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>24.800000000000011</v>
       </c>
-      <c r="AA81" s="25"/>
-      <c r="AB81" s="25"/>
+      <c r="AA81" s="15"/>
+      <c r="AB81" s="15"/>
       <c r="AC81" s="15">
+        <f t="shared" si="25"/>
+        <v>11</v>
+      </c>
+      <c r="AD81" s="15">
         <f t="shared" si="23"/>
-        <v>11</v>
-      </c>
-      <c r="AD81" s="15">
-        <f t="shared" si="21"/>
         <v>9.4303797468354418</v>
       </c>
       <c r="AE81" s="15">
@@ -16494,11 +16956,17 @@
       </c>
       <c r="AO81" s="15"/>
       <c r="AP81" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>8</v>
       </c>
-      <c r="AQ81" s="15"/>
-      <c r="AR81" s="15"/>
+      <c r="AQ81" s="15">
+        <f t="shared" si="27"/>
+        <v>5.2140000000000004</v>
+      </c>
+      <c r="AR81" s="15">
+        <f t="shared" si="28"/>
+        <v>5.94</v>
+      </c>
       <c r="AS81" s="15"/>
       <c r="AT81" s="15"/>
       <c r="AU81" s="15"/>
@@ -16540,7 +17008,7 @@
         <v>66</v>
       </c>
       <c r="L82" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-4</v>
       </c>
       <c r="M82" s="15"/>
@@ -16559,7 +17027,7 @@
       <c r="V82" s="15"/>
       <c r="W82" s="15"/>
       <c r="X82" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>12.4</v>
       </c>
       <c r="Y82" s="4">
@@ -16567,17 +17035,17 @@
         <v>29.599999999999994</v>
       </c>
       <c r="Z82" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29.599999999999994</v>
       </c>
-      <c r="AA82" s="25"/>
-      <c r="AB82" s="25"/>
+      <c r="AA82" s="15"/>
+      <c r="AB82" s="15"/>
       <c r="AC82" s="15">
+        <f t="shared" si="25"/>
+        <v>11</v>
+      </c>
+      <c r="AD82" s="15">
         <f t="shared" si="23"/>
-        <v>11</v>
-      </c>
-      <c r="AD82" s="15">
-        <f t="shared" si="21"/>
         <v>8.612903225806452</v>
       </c>
       <c r="AE82" s="15">
@@ -16612,11 +17080,17 @@
       </c>
       <c r="AO82" s="15"/>
       <c r="AP82" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>12</v>
       </c>
-      <c r="AQ82" s="15"/>
-      <c r="AR82" s="15"/>
+      <c r="AQ82" s="15">
+        <f t="shared" si="27"/>
+        <v>4.9600000000000009</v>
+      </c>
+      <c r="AR82" s="15">
+        <f t="shared" si="28"/>
+        <v>4.5600000000000005</v>
+      </c>
       <c r="AS82" s="15"/>
       <c r="AT82" s="15"/>
       <c r="AU82" s="15"/>
@@ -16654,7 +17128,7 @@
         <v>2</v>
       </c>
       <c r="L83" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="M83" s="15"/>
@@ -16675,26 +17149,26 @@
       </c>
       <c r="W83" s="15"/>
       <c r="X83" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y83" s="4">
         <v>20</v>
       </c>
       <c r="Z83" s="4">
-        <f t="shared" ref="Z83:Z84" si="26">Y83*1.5</f>
+        <f t="shared" ref="Z83:Z84" si="30">Y83*1.5</f>
         <v>30</v>
       </c>
-      <c r="AA83" s="25"/>
-      <c r="AB83" s="25"/>
+      <c r="AA83" s="15"/>
+      <c r="AB83" s="15"/>
       <c r="AC83" s="15" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD83" s="15" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD83" s="15" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AE83" s="15">
         <v>-0.6</v>
       </c>
@@ -16729,11 +17203,17 @@
         <v>132</v>
       </c>
       <c r="AP83" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
-      <c r="AQ83" s="15"/>
-      <c r="AR83" s="15"/>
+      <c r="AQ83" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR83" s="15">
+        <f t="shared" si="28"/>
+        <v>-0.21</v>
+      </c>
       <c r="AS83" s="15"/>
       <c r="AT83" s="15"/>
       <c r="AU83" s="15"/>
@@ -16775,7 +17255,7 @@
         <v>69</v>
       </c>
       <c r="L84" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-14</v>
       </c>
       <c r="M84" s="15"/>
@@ -16794,24 +17274,24 @@
       <c r="V84" s="15"/>
       <c r="W84" s="15"/>
       <c r="X84" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>11</v>
       </c>
       <c r="Y84" s="4">
         <v>10</v>
       </c>
       <c r="Z84" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
-      <c r="AA84" s="25"/>
-      <c r="AB84" s="25"/>
+      <c r="AA84" s="15"/>
+      <c r="AB84" s="15"/>
       <c r="AC84" s="15">
+        <f t="shared" si="25"/>
+        <v>12.509090909090911</v>
+      </c>
+      <c r="AD84" s="15">
         <f t="shared" si="23"/>
-        <v>12.509090909090911</v>
-      </c>
-      <c r="AD84" s="15">
-        <f t="shared" si="21"/>
         <v>11.145454545454548</v>
       </c>
       <c r="AE84" s="15">
@@ -16846,11 +17326,17 @@
       </c>
       <c r="AO84" s="15"/>
       <c r="AP84" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5</v>
       </c>
-      <c r="AQ84" s="15"/>
-      <c r="AR84" s="15"/>
+      <c r="AQ84" s="15">
+        <f t="shared" si="27"/>
+        <v>3.8499999999999996</v>
+      </c>
+      <c r="AR84" s="15">
+        <f t="shared" si="28"/>
+        <v>4.13</v>
+      </c>
       <c r="AS84" s="15"/>
       <c r="AT84" s="15"/>
       <c r="AU84" s="15"/>
@@ -16880,7 +17366,7 @@
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
       <c r="L85" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M85" s="11"/>
@@ -16899,24 +17385,24 @@
       <c r="V85" s="11"/>
       <c r="W85" s="11"/>
       <c r="X85" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y85" s="13"/>
       <c r="Z85" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="25"/>
-      <c r="AB85" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA85" s="15"/>
+      <c r="AB85" s="15"/>
       <c r="AC85" s="15" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD85" s="11" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD85" s="11" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AE85" s="11">
         <v>0</v>
       </c>
@@ -16951,11 +17437,17 @@
         <v>48</v>
       </c>
       <c r="AP85" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ85" s="15"/>
-      <c r="AR85" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR85" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS85" s="15"/>
       <c r="AT85" s="15"/>
       <c r="AU85" s="15"/>
@@ -16985,7 +17477,7 @@
       <c r="J86" s="11"/>
       <c r="K86" s="11"/>
       <c r="L86" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M86" s="11"/>
@@ -17004,24 +17496,24 @@
       <c r="V86" s="11"/>
       <c r="W86" s="11"/>
       <c r="X86" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y86" s="13"/>
       <c r="Z86" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA86" s="25"/>
-      <c r="AB86" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA86" s="15"/>
+      <c r="AB86" s="15"/>
       <c r="AC86" s="15" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD86" s="11" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD86" s="11" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AE86" s="11">
         <v>0</v>
       </c>
@@ -17056,11 +17548,17 @@
         <v>48</v>
       </c>
       <c r="AP86" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ86" s="15"/>
-      <c r="AR86" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR86" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS86" s="15"/>
       <c r="AT86" s="15"/>
       <c r="AU86" s="15"/>
@@ -17090,7 +17588,7 @@
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
       <c r="L87" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M87" s="11"/>
@@ -17109,24 +17607,24 @@
       <c r="V87" s="11"/>
       <c r="W87" s="11"/>
       <c r="X87" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y87" s="13"/>
       <c r="Z87" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="25"/>
-      <c r="AB87" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA87" s="15"/>
+      <c r="AB87" s="15"/>
       <c r="AC87" s="15" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD87" s="11" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD87" s="11" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AE87" s="11">
         <v>0</v>
       </c>
@@ -17161,11 +17659,17 @@
         <v>48</v>
       </c>
       <c r="AP87" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ87" s="15"/>
-      <c r="AR87" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR87" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS87" s="15"/>
       <c r="AT87" s="15"/>
       <c r="AU87" s="15"/>
@@ -17207,7 +17711,7 @@
         <v>137.5</v>
       </c>
       <c r="L88" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>5.1030000000000086</v>
       </c>
       <c r="M88" s="15"/>
@@ -17226,24 +17730,24 @@
       <c r="V88" s="15"/>
       <c r="W88" s="15"/>
       <c r="X88" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>28.520600000000002</v>
       </c>
       <c r="Y88" s="4"/>
       <c r="Z88" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="25"/>
-      <c r="AB88" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA88" s="15"/>
+      <c r="AB88" s="15"/>
       <c r="AC88" s="15">
+        <f t="shared" si="25"/>
+        <v>12.666360875998397</v>
+      </c>
+      <c r="AD88" s="15">
         <f t="shared" si="23"/>
         <v>12.666360875998397</v>
       </c>
-      <c r="AD88" s="15">
-        <f t="shared" si="21"/>
-        <v>12.666360875998397</v>
-      </c>
       <c r="AE88" s="15">
         <v>36.330599999999997</v>
       </c>
@@ -17276,11 +17780,17 @@
       </c>
       <c r="AO88" s="15"/>
       <c r="AP88" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ88" s="15"/>
-      <c r="AR88" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="15">
+        <f t="shared" si="27"/>
+        <v>28.520600000000002</v>
+      </c>
+      <c r="AR88" s="15">
+        <f t="shared" si="28"/>
+        <v>36.330599999999997</v>
+      </c>
       <c r="AS88" s="15"/>
       <c r="AT88" s="15"/>
       <c r="AU88" s="15"/>
@@ -17310,7 +17820,7 @@
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
       <c r="L89" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M89" s="11"/>
@@ -17329,24 +17839,24 @@
       <c r="V89" s="11"/>
       <c r="W89" s="11"/>
       <c r="X89" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y89" s="13"/>
       <c r="Z89" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="25"/>
-      <c r="AB89" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA89" s="15"/>
+      <c r="AB89" s="15"/>
       <c r="AC89" s="15" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD89" s="11" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD89" s="11" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AE89" s="11">
         <v>0</v>
       </c>
@@ -17381,11 +17891,17 @@
         <v>48</v>
       </c>
       <c r="AP89" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ89" s="15"/>
-      <c r="AR89" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ89" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR89" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS89" s="15"/>
       <c r="AT89" s="15"/>
       <c r="AU89" s="15"/>
@@ -17427,7 +17943,7 @@
         <v>1842.5</v>
       </c>
       <c r="L90" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-192.60200000000009</v>
       </c>
       <c r="M90" s="15"/>
@@ -17450,22 +17966,22 @@
         <v>300</v>
       </c>
       <c r="X90" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>329.9796</v>
       </c>
       <c r="Y90" s="4"/>
       <c r="Z90" s="4">
-        <f t="shared" ref="Z90:Z91" si="27">Y90+X90*$Z$1</f>
+        <f t="shared" ref="Z90:Z91" si="31">Y90+X90*$Z$1</f>
         <v>593.96328000000005</v>
       </c>
-      <c r="AA90" s="25"/>
-      <c r="AB90" s="25"/>
+      <c r="AA90" s="15"/>
+      <c r="AB90" s="15"/>
       <c r="AC90" s="15">
+        <f t="shared" si="25"/>
+        <v>11.519440232062831</v>
+      </c>
+      <c r="AD90" s="15">
         <f t="shared" si="23"/>
-        <v>11.519440232062831</v>
-      </c>
-      <c r="AD90" s="15">
-        <f t="shared" si="21"/>
         <v>9.7194402320628299</v>
       </c>
       <c r="AE90" s="15">
@@ -17500,11 +18016,17 @@
       </c>
       <c r="AO90" s="15"/>
       <c r="AP90" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>594</v>
       </c>
-      <c r="AQ90" s="15"/>
-      <c r="AR90" s="15"/>
+      <c r="AQ90" s="15">
+        <f t="shared" si="27"/>
+        <v>329.9796</v>
+      </c>
+      <c r="AR90" s="15">
+        <f t="shared" si="28"/>
+        <v>326.053</v>
+      </c>
       <c r="AS90" s="15"/>
       <c r="AT90" s="15"/>
       <c r="AU90" s="15"/>
@@ -17546,7 +18068,7 @@
         <v>1514.0160000000001</v>
       </c>
       <c r="L91" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-372.00200000000018</v>
       </c>
       <c r="M91" s="15"/>
@@ -17571,22 +18093,22 @@
         <v>210</v>
       </c>
       <c r="X91" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>228.40279999999998</v>
       </c>
       <c r="Y91" s="4"/>
       <c r="Z91" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>411.12503999999996</v>
       </c>
-      <c r="AA91" s="25"/>
-      <c r="AB91" s="25"/>
+      <c r="AA91" s="15"/>
+      <c r="AB91" s="15"/>
       <c r="AC91" s="15">
+        <f t="shared" si="25"/>
+        <v>13.24895596726485</v>
+      </c>
+      <c r="AD91" s="15">
         <f t="shared" si="23"/>
-        <v>13.24895596726485</v>
-      </c>
-      <c r="AD91" s="15">
-        <f t="shared" si="21"/>
         <v>11.448955967264849</v>
       </c>
       <c r="AE91" s="15">
@@ -17621,11 +18143,17 @@
       </c>
       <c r="AO91" s="15"/>
       <c r="AP91" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>411</v>
       </c>
-      <c r="AQ91" s="15"/>
-      <c r="AR91" s="15"/>
+      <c r="AQ91" s="15">
+        <f t="shared" si="27"/>
+        <v>228.40279999999998</v>
+      </c>
+      <c r="AR91" s="15">
+        <f t="shared" si="28"/>
+        <v>232.9778</v>
+      </c>
       <c r="AS91" s="15"/>
       <c r="AT91" s="15"/>
       <c r="AU91" s="15"/>
@@ -17667,7 +18195,7 @@
         <v>1949.8</v>
       </c>
       <c r="L92" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-1144.425</v>
       </c>
       <c r="M92" s="15"/>
@@ -17693,17 +18221,17 @@
         <v>330</v>
       </c>
       <c r="X92" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>161.07499999999999</v>
       </c>
       <c r="Y92" s="4"/>
       <c r="Z92" s="4">
         <v>1000</v>
       </c>
-      <c r="AA92" s="25"/>
-      <c r="AB92" s="25"/>
+      <c r="AA92" s="15"/>
+      <c r="AB92" s="15"/>
       <c r="AC92" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>29.247204097470121</v>
       </c>
       <c r="AD92" s="15">
@@ -17742,11 +18270,17 @@
       </c>
       <c r="AO92" s="15"/>
       <c r="AP92" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1000</v>
       </c>
-      <c r="AQ92" s="15"/>
-      <c r="AR92" s="15"/>
+      <c r="AQ92" s="15">
+        <f t="shared" si="27"/>
+        <v>161.07499999999999</v>
+      </c>
+      <c r="AR92" s="15">
+        <f t="shared" si="28"/>
+        <v>363.33519999999999</v>
+      </c>
       <c r="AS92" s="15"/>
       <c r="AT92" s="15"/>
       <c r="AU92" s="15"/>
@@ -17776,7 +18310,7 @@
       <c r="J93" s="11"/>
       <c r="K93" s="11"/>
       <c r="L93" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M93" s="11"/>
@@ -17795,22 +18329,22 @@
       <c r="V93" s="11"/>
       <c r="W93" s="11"/>
       <c r="X93" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y93" s="13"/>
       <c r="Z93" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="25"/>
-      <c r="AB93" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA93" s="15"/>
+      <c r="AB93" s="15"/>
       <c r="AC93" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD93" s="11" t="e">
-        <f t="shared" ref="AD93:AD122" si="28">(F93+O93+P93+R93+S93+T93+U93+V93+W93)/X93</f>
+        <f t="shared" ref="AD93:AD122" si="32">(F93+O93+P93+R93+S93+T93+U93+V93+W93)/X93</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AE93" s="11">
@@ -17847,11 +18381,17 @@
         <v>48</v>
       </c>
       <c r="AP93" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ93" s="15"/>
-      <c r="AR93" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR93" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS93" s="15"/>
       <c r="AT93" s="15"/>
       <c r="AU93" s="15"/>
@@ -17891,7 +18431,7 @@
         <v>23</v>
       </c>
       <c r="L94" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-25</v>
       </c>
       <c r="M94" s="15"/>
@@ -17912,7 +18452,7 @@
       <c r="V94" s="15"/>
       <c r="W94" s="15"/>
       <c r="X94" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-0.4</v>
       </c>
       <c r="Y94" s="4">
@@ -17922,14 +18462,14 @@
         <f>Y94*1.5</f>
         <v>30</v>
       </c>
-      <c r="AA94" s="25"/>
-      <c r="AB94" s="25"/>
+      <c r="AA94" s="15"/>
+      <c r="AB94" s="15"/>
       <c r="AC94" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-167.5</v>
       </c>
       <c r="AD94" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>-92.5</v>
       </c>
       <c r="AE94" s="15">
@@ -17964,11 +18504,17 @@
       </c>
       <c r="AO94" s="15"/>
       <c r="AP94" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>9</v>
       </c>
-      <c r="AQ94" s="15"/>
-      <c r="AR94" s="15"/>
+      <c r="AQ94" s="15">
+        <f t="shared" si="27"/>
+        <v>-0.12</v>
+      </c>
+      <c r="AR94" s="15">
+        <f t="shared" si="28"/>
+        <v>-0.48</v>
+      </c>
       <c r="AS94" s="15"/>
       <c r="AT94" s="15"/>
       <c r="AU94" s="15"/>
@@ -17998,7 +18544,7 @@
       <c r="J95" s="11"/>
       <c r="K95" s="11"/>
       <c r="L95" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M95" s="11"/>
@@ -18017,22 +18563,22 @@
       <c r="V95" s="11"/>
       <c r="W95" s="11"/>
       <c r="X95" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y95" s="13"/>
       <c r="Z95" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="25"/>
-      <c r="AB95" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA95" s="15"/>
+      <c r="AB95" s="15"/>
       <c r="AC95" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD95" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE95" s="11">
@@ -18069,11 +18615,17 @@
         <v>48</v>
       </c>
       <c r="AP95" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ95" s="15"/>
-      <c r="AR95" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ95" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR95" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS95" s="15"/>
       <c r="AT95" s="15"/>
       <c r="AU95" s="15"/>
@@ -18111,7 +18663,7 @@
         <v>89</v>
       </c>
       <c r="L96" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-89</v>
       </c>
       <c r="M96" s="15"/>
@@ -18132,24 +18684,24 @@
       </c>
       <c r="W96" s="15"/>
       <c r="X96" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y96" s="4">
         <v>60</v>
       </c>
       <c r="Z96" s="4">
-        <f t="shared" ref="Z96:Z98" si="29">Y96*1.5</f>
+        <f t="shared" ref="Z96:Z98" si="33">Y96*1.5</f>
         <v>90</v>
       </c>
-      <c r="AA96" s="25"/>
-      <c r="AB96" s="25"/>
+      <c r="AA96" s="15"/>
+      <c r="AB96" s="15"/>
       <c r="AC96" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD96" s="15" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE96" s="15">
@@ -18186,11 +18738,17 @@
         <v>146</v>
       </c>
       <c r="AP96" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>6</v>
       </c>
-      <c r="AQ96" s="15"/>
-      <c r="AR96" s="15"/>
+      <c r="AQ96" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR96" s="15">
+        <f t="shared" si="28"/>
+        <v>0.47600000000000003</v>
+      </c>
       <c r="AS96" s="15"/>
       <c r="AT96" s="15"/>
       <c r="AU96" s="15"/>
@@ -18232,7 +18790,7 @@
         <v>115</v>
       </c>
       <c r="L97" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-39</v>
       </c>
       <c r="M97" s="15"/>
@@ -18253,24 +18811,24 @@
       </c>
       <c r="W97" s="15"/>
       <c r="X97" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>15.2</v>
       </c>
       <c r="Y97" s="4">
         <v>40</v>
       </c>
       <c r="Z97" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>60</v>
       </c>
-      <c r="AA97" s="25"/>
-      <c r="AB97" s="25"/>
+      <c r="AA97" s="15"/>
+      <c r="AB97" s="15"/>
       <c r="AC97" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>14.552631578947375</v>
       </c>
       <c r="AD97" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>10.605263157894743</v>
       </c>
       <c r="AE97" s="15">
@@ -18307,11 +18865,17 @@
         <v>146</v>
       </c>
       <c r="AP97" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="AQ97" s="15"/>
-      <c r="AR97" s="15"/>
+      <c r="AQ97" s="15">
+        <f t="shared" si="27"/>
+        <v>1.0640000000000001</v>
+      </c>
+      <c r="AR97" s="15">
+        <f t="shared" si="28"/>
+        <v>1.7220000000000002</v>
+      </c>
       <c r="AS97" s="15"/>
       <c r="AT97" s="15"/>
       <c r="AU97" s="15"/>
@@ -18353,7 +18917,7 @@
         <v>90</v>
       </c>
       <c r="L98" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-15</v>
       </c>
       <c r="M98" s="15"/>
@@ -18374,24 +18938,24 @@
       </c>
       <c r="W98" s="15"/>
       <c r="X98" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="Y98" s="4">
         <v>50</v>
       </c>
       <c r="Z98" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>75</v>
       </c>
-      <c r="AA98" s="25"/>
-      <c r="AB98" s="25"/>
+      <c r="AA98" s="15"/>
+      <c r="AB98" s="15"/>
       <c r="AC98" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>16.146666666666665</v>
       </c>
       <c r="AD98" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>11.146666666666667</v>
       </c>
       <c r="AE98" s="15">
@@ -18428,11 +18992,17 @@
         <v>146</v>
       </c>
       <c r="AP98" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5</v>
       </c>
-      <c r="AQ98" s="15"/>
-      <c r="AR98" s="15"/>
+      <c r="AQ98" s="15">
+        <f t="shared" si="27"/>
+        <v>1.05</v>
+      </c>
+      <c r="AR98" s="15">
+        <f t="shared" si="28"/>
+        <v>1.8900000000000001</v>
+      </c>
       <c r="AS98" s="15"/>
       <c r="AT98" s="15"/>
       <c r="AU98" s="15"/>
@@ -18470,7 +19040,7 @@
         <v>18</v>
       </c>
       <c r="L99" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-18</v>
       </c>
       <c r="M99" s="11"/>
@@ -18489,22 +19059,22 @@
       <c r="V99" s="11"/>
       <c r="W99" s="11"/>
       <c r="X99" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y99" s="13"/>
       <c r="Z99" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="25"/>
-      <c r="AB99" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA99" s="15"/>
+      <c r="AB99" s="15"/>
       <c r="AC99" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD99" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE99" s="11">
@@ -18539,11 +19109,17 @@
       </c>
       <c r="AO99" s="11"/>
       <c r="AP99" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ99" s="15"/>
-      <c r="AR99" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR99" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS99" s="15"/>
       <c r="AT99" s="15"/>
       <c r="AU99" s="15"/>
@@ -18581,7 +19157,7 @@
         <v>68</v>
       </c>
       <c r="L100" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-5</v>
       </c>
       <c r="M100" s="15"/>
@@ -18600,22 +19176,22 @@
       <c r="V100" s="15"/>
       <c r="W100" s="15"/>
       <c r="X100" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>12.6</v>
       </c>
       <c r="Y100" s="4"/>
       <c r="Z100" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="25"/>
-      <c r="AB100" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA100" s="15"/>
+      <c r="AB100" s="15"/>
       <c r="AC100" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>11.190476190476192</v>
       </c>
       <c r="AD100" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>11.190476190476192</v>
       </c>
       <c r="AE100" s="15">
@@ -18652,11 +19228,17 @@
         <v>127</v>
       </c>
       <c r="AP100" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ100" s="15"/>
-      <c r="AR100" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ100" s="15">
+        <f t="shared" si="27"/>
+        <v>3.78</v>
+      </c>
+      <c r="AR100" s="15">
+        <f t="shared" si="28"/>
+        <v>4.74</v>
+      </c>
       <c r="AS100" s="15"/>
       <c r="AT100" s="15"/>
       <c r="AU100" s="15"/>
@@ -18696,7 +19278,7 @@
         <v>10.8</v>
       </c>
       <c r="L101" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>-4.7030000000000003</v>
       </c>
       <c r="M101" s="15"/>
@@ -18715,7 +19297,7 @@
       <c r="V101" s="15"/>
       <c r="W101" s="15"/>
       <c r="X101" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.2194</v>
       </c>
       <c r="Y101" s="4"/>
@@ -18723,14 +19305,14 @@
         <f>Y101*1.5</f>
         <v>0</v>
       </c>
-      <c r="AA101" s="25"/>
-      <c r="AB101" s="25"/>
+      <c r="AA101" s="15"/>
+      <c r="AB101" s="15"/>
       <c r="AC101" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>20.018369690011472</v>
       </c>
       <c r="AD101" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>20.018369690011472</v>
       </c>
       <c r="AE101" s="15">
@@ -18767,11 +19349,17 @@
         <v>152</v>
       </c>
       <c r="AP101" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ101" s="15"/>
-      <c r="AR101" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="15">
+        <f t="shared" si="27"/>
+        <v>1.2194</v>
+      </c>
+      <c r="AR101" s="15">
+        <f t="shared" si="28"/>
+        <v>2.0341999999999998</v>
+      </c>
       <c r="AS101" s="15"/>
       <c r="AT101" s="15"/>
       <c r="AU101" s="15"/>
@@ -18811,7 +19399,7 @@
         <v>57</v>
       </c>
       <c r="L102" s="15">
-        <f t="shared" ref="L102:L132" si="30">E102-K102</f>
+        <f t="shared" ref="L102:L132" si="34">E102-K102</f>
         <v>-55</v>
       </c>
       <c r="M102" s="15"/>
@@ -18830,22 +19418,22 @@
       <c r="V102" s="15"/>
       <c r="W102" s="15"/>
       <c r="X102" s="15">
-        <f t="shared" ref="X102:X132" si="31">E102/5</f>
+        <f t="shared" ref="X102:X132" si="35">E102/5</f>
         <v>0.4</v>
       </c>
       <c r="Y102" s="4"/>
       <c r="Z102" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA102" s="25"/>
-      <c r="AB102" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA102" s="15"/>
+      <c r="AB102" s="15"/>
       <c r="AC102" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>302.5</v>
       </c>
       <c r="AD102" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>302.5</v>
       </c>
       <c r="AE102" s="15">
@@ -18882,11 +19470,17 @@
         <v>186</v>
       </c>
       <c r="AP102" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ102" s="15"/>
-      <c r="AR102" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="15">
+        <f t="shared" si="27"/>
+        <v>4.4000000000000004E-2</v>
+      </c>
+      <c r="AR102" s="15">
+        <f t="shared" si="28"/>
+        <v>1.21</v>
+      </c>
       <c r="AS102" s="15"/>
       <c r="AT102" s="15"/>
       <c r="AU102" s="15"/>
@@ -18916,7 +19510,7 @@
       <c r="J103" s="11"/>
       <c r="K103" s="11"/>
       <c r="L103" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M103" s="11"/>
@@ -18935,22 +19529,22 @@
       <c r="V103" s="11"/>
       <c r="W103" s="11"/>
       <c r="X103" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y103" s="13"/>
       <c r="Z103" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="25"/>
-      <c r="AB103" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA103" s="15"/>
+      <c r="AB103" s="15"/>
       <c r="AC103" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD103" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE103" s="11">
@@ -18987,11 +19581,17 @@
         <v>48</v>
       </c>
       <c r="AP103" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ103" s="15"/>
-      <c r="AR103" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ103" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR103" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS103" s="15"/>
       <c r="AT103" s="15"/>
       <c r="AU103" s="15"/>
@@ -19033,7 +19633,7 @@
         <v>104</v>
       </c>
       <c r="L104" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-14</v>
       </c>
       <c r="M104" s="15"/>
@@ -19052,22 +19652,22 @@
       <c r="V104" s="15"/>
       <c r="W104" s="15"/>
       <c r="X104" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>18</v>
       </c>
       <c r="Y104" s="4"/>
       <c r="Z104" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="25"/>
-      <c r="AB104" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA104" s="15"/>
+      <c r="AB104" s="15"/>
       <c r="AC104" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>13.799999999999995</v>
       </c>
       <c r="AD104" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>13.799999999999995</v>
       </c>
       <c r="AE104" s="15">
@@ -19102,11 +19702,17 @@
       </c>
       <c r="AO104" s="15"/>
       <c r="AP104" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ104" s="15"/>
-      <c r="AR104" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ104" s="15">
+        <f t="shared" si="27"/>
+        <v>1.44</v>
+      </c>
+      <c r="AR104" s="15">
+        <f t="shared" si="28"/>
+        <v>1.952</v>
+      </c>
       <c r="AS104" s="15"/>
       <c r="AT104" s="15"/>
       <c r="AU104" s="15"/>
@@ -19148,7 +19754,7 @@
         <v>65</v>
       </c>
       <c r="L105" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-9</v>
       </c>
       <c r="M105" s="15"/>
@@ -19167,7 +19773,7 @@
       <c r="V105" s="15"/>
       <c r="W105" s="15"/>
       <c r="X105" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>11.2</v>
       </c>
       <c r="Y105" s="4"/>
@@ -19175,20 +19781,20 @@
         <f>AA105</f>
         <v>50</v>
       </c>
-      <c r="AA105" s="25">
+      <c r="AA105" s="15">
         <f>VLOOKUP(A105,[1]Sheet!$A:$AA,26,0)</f>
         <v>50</v>
       </c>
-      <c r="AB105" s="25" t="str">
+      <c r="AB105" s="15" t="str">
         <f>VLOOKUP(A105,[1]Sheet!$A:$AA,27,0)</f>
         <v>Востребован продукт</v>
       </c>
       <c r="AC105" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>21.428571428571431</v>
       </c>
       <c r="AD105" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>16.964285714285715</v>
       </c>
       <c r="AE105" s="15">
@@ -19223,11 +19829,17 @@
       </c>
       <c r="AO105" s="15"/>
       <c r="AP105" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="AQ105" s="15"/>
-      <c r="AR105" s="15"/>
+      <c r="AQ105" s="15">
+        <f t="shared" si="27"/>
+        <v>0.89599999999999991</v>
+      </c>
+      <c r="AR105" s="15">
+        <f t="shared" si="28"/>
+        <v>1.44</v>
+      </c>
       <c r="AS105" s="15"/>
       <c r="AT105" s="15"/>
       <c r="AU105" s="15"/>
@@ -19267,7 +19879,7 @@
         <v>10</v>
       </c>
       <c r="L106" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-9</v>
       </c>
       <c r="M106" s="15"/>
@@ -19286,22 +19898,22 @@
       <c r="V106" s="15"/>
       <c r="W106" s="15"/>
       <c r="X106" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0.2</v>
       </c>
       <c r="Y106" s="4"/>
       <c r="Z106" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="25"/>
-      <c r="AB106" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA106" s="15"/>
+      <c r="AB106" s="15"/>
       <c r="AC106" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>290</v>
       </c>
       <c r="AD106" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>290</v>
       </c>
       <c r="AE106" s="15">
@@ -19338,11 +19950,17 @@
         <v>187</v>
       </c>
       <c r="AP106" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ106" s="15"/>
-      <c r="AR106" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ106" s="15">
+        <f t="shared" si="27"/>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="AR106" s="15">
+        <f t="shared" si="28"/>
+        <v>0.17</v>
+      </c>
       <c r="AS106" s="15"/>
       <c r="AT106" s="15"/>
       <c r="AU106" s="15"/>
@@ -19384,7 +20002,7 @@
         <v>91.2</v>
       </c>
       <c r="L107" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-26.215000000000003</v>
       </c>
       <c r="M107" s="15"/>
@@ -19403,7 +20021,7 @@
       <c r="V107" s="15"/>
       <c r="W107" s="15"/>
       <c r="X107" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>12.997</v>
       </c>
       <c r="Y107" s="4">
@@ -19411,23 +20029,23 @@
         <v>31.155999999999985</v>
       </c>
       <c r="Z107" s="4">
-        <f t="shared" ref="Z107:Z109" si="32">AA107</f>
+        <f t="shared" ref="Z107:Z109" si="36">AA107</f>
         <v>250</v>
       </c>
-      <c r="AA107" s="25">
+      <c r="AA107" s="15">
         <f>VLOOKUP(A107,[1]Sheet!$A:$AA,26,0)</f>
         <v>250</v>
       </c>
-      <c r="AB107" s="25" t="str">
+      <c r="AB107" s="15" t="str">
         <f>VLOOKUP(A107,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250кг, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="AC107" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>27.838039547587908</v>
       </c>
       <c r="AD107" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>8.6028314226359939</v>
       </c>
       <c r="AE107" s="15">
@@ -19462,11 +20080,17 @@
       </c>
       <c r="AO107" s="15"/>
       <c r="AP107" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>250</v>
       </c>
-      <c r="AQ107" s="15"/>
-      <c r="AR107" s="15"/>
+      <c r="AQ107" s="15">
+        <f t="shared" si="27"/>
+        <v>12.997</v>
+      </c>
+      <c r="AR107" s="15">
+        <f t="shared" si="28"/>
+        <v>22.168800000000001</v>
+      </c>
       <c r="AS107" s="15"/>
       <c r="AT107" s="15"/>
       <c r="AU107" s="15"/>
@@ -19508,7 +20132,7 @@
         <v>114.7</v>
       </c>
       <c r="L108" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-32.366</v>
       </c>
       <c r="M108" s="15"/>
@@ -19527,7 +20151,7 @@
       <c r="V108" s="15"/>
       <c r="W108" s="15"/>
       <c r="X108" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>16.466799999999999</v>
       </c>
       <c r="Y108" s="4">
@@ -19535,23 +20159,23 @@
         <v>86.229799999999983</v>
       </c>
       <c r="Z108" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>250</v>
       </c>
-      <c r="AA108" s="25">
+      <c r="AA108" s="15">
         <f>VLOOKUP(A108,[1]Sheet!$A:$AA,26,0)</f>
         <v>250</v>
       </c>
-      <c r="AB108" s="25" t="str">
+      <c r="AB108" s="15" t="str">
         <f>VLOOKUP(A108,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250кг, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="AC108" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>20.945478174265794</v>
       </c>
       <c r="AD108" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.7634148711346471</v>
       </c>
       <c r="AE108" s="15">
@@ -19586,11 +20210,17 @@
       </c>
       <c r="AO108" s="15"/>
       <c r="AP108" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>250</v>
       </c>
-      <c r="AQ108" s="15"/>
-      <c r="AR108" s="15"/>
+      <c r="AQ108" s="15">
+        <f t="shared" si="27"/>
+        <v>16.466799999999999</v>
+      </c>
+      <c r="AR108" s="15">
+        <f t="shared" si="28"/>
+        <v>7.055200000000001</v>
+      </c>
       <c r="AS108" s="15"/>
       <c r="AT108" s="15"/>
       <c r="AU108" s="15"/>
@@ -19630,7 +20260,7 @@
         <v>55.5</v>
       </c>
       <c r="L109" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-59.061999999999998</v>
       </c>
       <c r="M109" s="15"/>
@@ -19653,30 +20283,30 @@
       </c>
       <c r="W109" s="15"/>
       <c r="X109" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.71239999999999992</v>
       </c>
       <c r="Y109" s="4">
         <v>60</v>
       </c>
       <c r="Z109" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>250</v>
       </c>
-      <c r="AA109" s="25">
+      <c r="AA109" s="15">
         <f>VLOOKUP(A109,[1]Sheet!$A:$AA,26,0)</f>
         <v>250</v>
       </c>
-      <c r="AB109" s="25" t="str">
+      <c r="AB109" s="15" t="str">
         <f>VLOOKUP(A109,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250кг, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="AC109" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-345.26670409882092</v>
       </c>
       <c r="AD109" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.6597417181358747</v>
       </c>
       <c r="AE109" s="15">
@@ -19711,11 +20341,17 @@
       </c>
       <c r="AO109" s="15"/>
       <c r="AP109" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>250</v>
       </c>
-      <c r="AQ109" s="15"/>
-      <c r="AR109" s="15"/>
+      <c r="AQ109" s="15">
+        <f t="shared" si="27"/>
+        <v>-0.71239999999999992</v>
+      </c>
+      <c r="AR109" s="15">
+        <f t="shared" si="28"/>
+        <v>-0.42520000000000002</v>
+      </c>
       <c r="AS109" s="15"/>
       <c r="AT109" s="15"/>
       <c r="AU109" s="15"/>
@@ -19745,7 +20381,7 @@
       <c r="J110" s="11"/>
       <c r="K110" s="11"/>
       <c r="L110" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M110" s="11"/>
@@ -19764,22 +20400,22 @@
       <c r="V110" s="11"/>
       <c r="W110" s="11"/>
       <c r="X110" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y110" s="13"/>
       <c r="Z110" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="25"/>
-      <c r="AB110" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA110" s="15"/>
+      <c r="AB110" s="15"/>
       <c r="AC110" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD110" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE110" s="11">
@@ -19816,11 +20452,17 @@
         <v>48</v>
       </c>
       <c r="AP110" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ110" s="15"/>
-      <c r="AR110" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ110" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR110" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS110" s="15"/>
       <c r="AT110" s="15"/>
       <c r="AU110" s="15"/>
@@ -19850,7 +20492,7 @@
       <c r="J111" s="11"/>
       <c r="K111" s="11"/>
       <c r="L111" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M111" s="11"/>
@@ -19869,22 +20511,22 @@
       <c r="V111" s="11"/>
       <c r="W111" s="11"/>
       <c r="X111" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y111" s="13"/>
       <c r="Z111" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA111" s="25"/>
-      <c r="AB111" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA111" s="15"/>
+      <c r="AB111" s="15"/>
       <c r="AC111" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD111" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE111" s="11">
@@ -19921,11 +20563,17 @@
         <v>48</v>
       </c>
       <c r="AP111" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ111" s="15"/>
-      <c r="AR111" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ111" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR111" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS111" s="15"/>
       <c r="AT111" s="15"/>
       <c r="AU111" s="15"/>
@@ -19965,7 +20613,7 @@
         <v>197</v>
       </c>
       <c r="L112" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-131</v>
       </c>
       <c r="M112" s="15"/>
@@ -19984,30 +20632,30 @@
       <c r="V112" s="15"/>
       <c r="W112" s="15"/>
       <c r="X112" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>13.2</v>
       </c>
       <c r="Y112" s="4">
         <v>50</v>
       </c>
       <c r="Z112" s="4">
-        <f t="shared" ref="Z112:Z114" si="33">AA112</f>
+        <f t="shared" ref="Z112:Z114" si="37">AA112</f>
         <v>250</v>
       </c>
-      <c r="AA112" s="25">
+      <c r="AA112" s="15">
         <f>VLOOKUP(A112,[1]Sheet!$A:$AA,26,0)</f>
         <v>250</v>
       </c>
-      <c r="AB112" s="25" t="str">
+      <c r="AB112" s="15" t="str">
         <f>VLOOKUP(A112,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250ШТ, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="AC112" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>34.393939393939398</v>
       </c>
       <c r="AD112" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>15.454545454545455</v>
       </c>
       <c r="AE112" s="15">
@@ -20042,11 +20690,17 @@
       </c>
       <c r="AO112" s="15"/>
       <c r="AP112" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70</v>
       </c>
-      <c r="AQ112" s="15"/>
-      <c r="AR112" s="15"/>
+      <c r="AQ112" s="15">
+        <f t="shared" si="27"/>
+        <v>3.6960000000000002</v>
+      </c>
+      <c r="AR112" s="15">
+        <f t="shared" si="28"/>
+        <v>6.4960000000000004</v>
+      </c>
       <c r="AS112" s="15"/>
       <c r="AT112" s="15"/>
       <c r="AU112" s="15"/>
@@ -20086,7 +20740,7 @@
         <v>183</v>
       </c>
       <c r="L113" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-111</v>
       </c>
       <c r="M113" s="15"/>
@@ -20105,28 +20759,28 @@
       <c r="V113" s="15"/>
       <c r="W113" s="15"/>
       <c r="X113" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>14.4</v>
       </c>
       <c r="Y113" s="4"/>
       <c r="Z113" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>250</v>
       </c>
-      <c r="AA113" s="25">
+      <c r="AA113" s="15">
         <f>VLOOKUP(A113,[1]Sheet!$A:$AA,26,0)</f>
         <v>250</v>
       </c>
-      <c r="AB113" s="25" t="str">
+      <c r="AB113" s="15" t="str">
         <f>VLOOKUP(A113,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250ШТ, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="AC113" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>38.333333333333336</v>
       </c>
       <c r="AD113" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>20.972222222222221</v>
       </c>
       <c r="AE113" s="15">
@@ -20161,11 +20815,17 @@
       </c>
       <c r="AO113" s="15"/>
       <c r="AP113" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70</v>
       </c>
-      <c r="AQ113" s="15"/>
-      <c r="AR113" s="15"/>
+      <c r="AQ113" s="15">
+        <f t="shared" si="27"/>
+        <v>4.0320000000000009</v>
+      </c>
+      <c r="AR113" s="15">
+        <f t="shared" si="28"/>
+        <v>7.0000000000000009</v>
+      </c>
       <c r="AS113" s="15"/>
       <c r="AT113" s="15"/>
       <c r="AU113" s="15"/>
@@ -20205,7 +20865,7 @@
         <v>206</v>
       </c>
       <c r="L114" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-160</v>
       </c>
       <c r="M114" s="15"/>
@@ -20226,30 +20886,30 @@
       <c r="V114" s="15"/>
       <c r="W114" s="15"/>
       <c r="X114" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="Y114" s="4">
         <v>100</v>
       </c>
       <c r="Z114" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>250</v>
       </c>
-      <c r="AA114" s="25">
+      <c r="AA114" s="15">
         <f>VLOOKUP(A114,[1]Sheet!$A:$AA,26,0)</f>
         <v>250</v>
       </c>
-      <c r="AB114" s="25" t="str">
+      <c r="AB114" s="15" t="str">
         <f>VLOOKUP(A114,[1]Sheet!$A:$AA,27,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250ШТ, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="AC114" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>42.717391304347828</v>
       </c>
       <c r="AD114" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>15.543478260869566</v>
       </c>
       <c r="AE114" s="15">
@@ -20284,11 +20944,17 @@
       </c>
       <c r="AO114" s="15"/>
       <c r="AP114" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>70</v>
       </c>
-      <c r="AQ114" s="15"/>
-      <c r="AR114" s="15"/>
+      <c r="AQ114" s="15">
+        <f t="shared" si="27"/>
+        <v>2.5760000000000001</v>
+      </c>
+      <c r="AR114" s="15">
+        <f t="shared" si="28"/>
+        <v>5.4880000000000013</v>
+      </c>
       <c r="AS114" s="15"/>
       <c r="AT114" s="15"/>
       <c r="AU114" s="15"/>
@@ -20330,7 +20996,7 @@
         <v>71</v>
       </c>
       <c r="L115" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-27</v>
       </c>
       <c r="M115" s="15"/>
@@ -20349,22 +21015,22 @@
       <c r="V115" s="15"/>
       <c r="W115" s="15"/>
       <c r="X115" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="Y115" s="4"/>
       <c r="Z115" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA115" s="25"/>
-      <c r="AB115" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA115" s="15"/>
+      <c r="AB115" s="15"/>
       <c r="AC115" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>15.090909090909092</v>
       </c>
       <c r="AD115" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>15.090909090909092</v>
       </c>
       <c r="AE115" s="15">
@@ -20399,11 +21065,17 @@
       </c>
       <c r="AO115" s="15"/>
       <c r="AP115" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ115" s="15"/>
-      <c r="AR115" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ115" s="15">
+        <f t="shared" si="27"/>
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="AR115" s="15">
+        <f t="shared" si="28"/>
+        <v>1.1159999999999999</v>
+      </c>
       <c r="AS115" s="15"/>
       <c r="AT115" s="15"/>
       <c r="AU115" s="15"/>
@@ -20443,7 +21115,7 @@
         <v>57.5</v>
       </c>
       <c r="L116" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-4.7389999999999972</v>
       </c>
       <c r="M116" s="15"/>
@@ -20462,25 +21134,25 @@
       <c r="V116" s="15"/>
       <c r="W116" s="15"/>
       <c r="X116" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>10.552200000000001</v>
       </c>
       <c r="Y116" s="4">
-        <f t="shared" ref="Y116:Y122" si="34">11*X116-W116-V116-U116-T116-S116-R116-P116-O116-F116</f>
+        <f t="shared" ref="Y116:Y122" si="38">11*X116-W116-V116-U116-T116-S116-R116-P116-O116-F116</f>
         <v>18.379400000000011</v>
       </c>
       <c r="Z116" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>18.379400000000011</v>
       </c>
-      <c r="AA116" s="25"/>
-      <c r="AB116" s="25"/>
+      <c r="AA116" s="15"/>
+      <c r="AB116" s="15"/>
       <c r="AC116" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>10.999999999999998</v>
       </c>
       <c r="AD116" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>9.2582399878698265</v>
       </c>
       <c r="AE116" s="15">
@@ -20515,11 +21187,17 @@
       </c>
       <c r="AO116" s="15"/>
       <c r="AP116" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>18</v>
       </c>
-      <c r="AQ116" s="15"/>
-      <c r="AR116" s="15"/>
+      <c r="AQ116" s="15">
+        <f t="shared" si="27"/>
+        <v>10.552200000000001</v>
+      </c>
+      <c r="AR116" s="15">
+        <f t="shared" si="28"/>
+        <v>11.1274</v>
+      </c>
       <c r="AS116" s="15"/>
       <c r="AT116" s="15"/>
       <c r="AU116" s="15"/>
@@ -20561,7 +21239,7 @@
         <v>105</v>
       </c>
       <c r="L117" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-11.715999999999994</v>
       </c>
       <c r="M117" s="15"/>
@@ -20580,25 +21258,25 @@
       <c r="V117" s="15"/>
       <c r="W117" s="15"/>
       <c r="X117" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>18.6568</v>
       </c>
       <c r="Y117" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>47.601800000000019</v>
       </c>
       <c r="Z117" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>47.601800000000019</v>
       </c>
-      <c r="AA117" s="25"/>
-      <c r="AB117" s="25"/>
+      <c r="AA117" s="15"/>
+      <c r="AB117" s="15"/>
       <c r="AC117" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>11</v>
       </c>
       <c r="AD117" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>8.448554950473822</v>
       </c>
       <c r="AE117" s="15">
@@ -20633,11 +21311,17 @@
       </c>
       <c r="AO117" s="15"/>
       <c r="AP117" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>48</v>
       </c>
-      <c r="AQ117" s="15"/>
-      <c r="AR117" s="15"/>
+      <c r="AQ117" s="15">
+        <f t="shared" si="27"/>
+        <v>18.6568</v>
+      </c>
+      <c r="AR117" s="15">
+        <f t="shared" si="28"/>
+        <v>16.679200000000002</v>
+      </c>
       <c r="AS117" s="15"/>
       <c r="AT117" s="15"/>
       <c r="AU117" s="15"/>
@@ -20679,7 +21363,7 @@
         <v>50</v>
       </c>
       <c r="L118" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-32</v>
       </c>
       <c r="M118" s="15"/>
@@ -20698,22 +21382,22 @@
       <c r="V118" s="15"/>
       <c r="W118" s="15"/>
       <c r="X118" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3.6</v>
       </c>
       <c r="Y118" s="4"/>
       <c r="Z118" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA118" s="25"/>
-      <c r="AB118" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA118" s="15"/>
+      <c r="AB118" s="15"/>
       <c r="AC118" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>37.222222222222221</v>
       </c>
       <c r="AD118" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>37.222222222222221</v>
       </c>
       <c r="AE118" s="15">
@@ -20748,11 +21432,17 @@
       </c>
       <c r="AO118" s="15"/>
       <c r="AP118" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ118" s="15"/>
-      <c r="AR118" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ118" s="15">
+        <f t="shared" si="27"/>
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="AR118" s="15">
+        <f t="shared" si="28"/>
+        <v>0.75600000000000001</v>
+      </c>
       <c r="AS118" s="15"/>
       <c r="AT118" s="15"/>
       <c r="AU118" s="15"/>
@@ -20794,7 +21484,7 @@
         <v>52</v>
       </c>
       <c r="L119" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-32</v>
       </c>
       <c r="M119" s="15"/>
@@ -20813,22 +21503,22 @@
       <c r="V119" s="15"/>
       <c r="W119" s="15"/>
       <c r="X119" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>4</v>
       </c>
       <c r="Y119" s="4"/>
       <c r="Z119" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" s="25"/>
-      <c r="AB119" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA119" s="15"/>
+      <c r="AB119" s="15"/>
       <c r="AC119" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>35.5</v>
       </c>
       <c r="AD119" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>35.5</v>
       </c>
       <c r="AE119" s="15">
@@ -20863,11 +21553,17 @@
       </c>
       <c r="AO119" s="15"/>
       <c r="AP119" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ119" s="15"/>
-      <c r="AR119" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ119" s="15">
+        <f t="shared" si="27"/>
+        <v>0.36</v>
+      </c>
+      <c r="AR119" s="15">
+        <f t="shared" si="28"/>
+        <v>0.99</v>
+      </c>
       <c r="AS119" s="15"/>
       <c r="AT119" s="15"/>
       <c r="AU119" s="15"/>
@@ -20909,7 +21605,7 @@
         <v>77.5</v>
       </c>
       <c r="L120" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-13.505000000000003</v>
       </c>
       <c r="M120" s="15"/>
@@ -20928,22 +21624,22 @@
       <c r="V120" s="15"/>
       <c r="W120" s="15"/>
       <c r="X120" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>12.798999999999999</v>
       </c>
       <c r="Y120" s="4"/>
       <c r="Z120" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" s="25"/>
-      <c r="AB120" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA120" s="15"/>
+      <c r="AB120" s="15"/>
       <c r="AC120" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>14.62826783342449</v>
       </c>
       <c r="AD120" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>14.62826783342449</v>
       </c>
       <c r="AE120" s="15">
@@ -20978,11 +21674,17 @@
       </c>
       <c r="AO120" s="15"/>
       <c r="AP120" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ120" s="15"/>
-      <c r="AR120" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ120" s="15">
+        <f t="shared" si="27"/>
+        <v>12.798999999999999</v>
+      </c>
+      <c r="AR120" s="15">
+        <f t="shared" si="28"/>
+        <v>18.248999999999999</v>
+      </c>
       <c r="AS120" s="15"/>
       <c r="AT120" s="15"/>
       <c r="AU120" s="15"/>
@@ -21024,7 +21726,7 @@
         <v>260.39999999999998</v>
       </c>
       <c r="L121" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-42.418999999999983</v>
       </c>
       <c r="M121" s="15"/>
@@ -21043,22 +21745,22 @@
       <c r="V121" s="15"/>
       <c r="W121" s="15"/>
       <c r="X121" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>43.596199999999996</v>
       </c>
       <c r="Y121" s="4"/>
       <c r="Z121" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" s="25"/>
-      <c r="AB121" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA121" s="15"/>
+      <c r="AB121" s="15"/>
       <c r="AC121" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>13.44982360847964</v>
       </c>
       <c r="AD121" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>13.44982360847964</v>
       </c>
       <c r="AE121" s="15">
@@ -21093,11 +21795,17 @@
       </c>
       <c r="AO121" s="15"/>
       <c r="AP121" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ121" s="15"/>
-      <c r="AR121" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ121" s="15">
+        <f t="shared" si="27"/>
+        <v>43.596199999999996</v>
+      </c>
+      <c r="AR121" s="15">
+        <f t="shared" si="28"/>
+        <v>48.666800000000002</v>
+      </c>
       <c r="AS121" s="15"/>
       <c r="AT121" s="15"/>
       <c r="AU121" s="15"/>
@@ -21137,7 +21845,7 @@
         <v>52.1</v>
       </c>
       <c r="L122" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>2.4769999999999968</v>
       </c>
       <c r="M122" s="15"/>
@@ -21156,25 +21864,25 @@
       <c r="V122" s="15"/>
       <c r="W122" s="15"/>
       <c r="X122" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>10.9154</v>
       </c>
       <c r="Y122" s="4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>12.753199999999996</v>
       </c>
       <c r="Z122" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>12.753199999999996</v>
       </c>
-      <c r="AA122" s="25"/>
-      <c r="AB122" s="25"/>
+      <c r="AA122" s="15"/>
+      <c r="AB122" s="15"/>
       <c r="AC122" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>11</v>
       </c>
       <c r="AD122" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>9.8316323726111747</v>
       </c>
       <c r="AE122" s="15">
@@ -21209,11 +21917,17 @@
       </c>
       <c r="AO122" s="15"/>
       <c r="AP122" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>13</v>
       </c>
-      <c r="AQ122" s="15"/>
-      <c r="AR122" s="15"/>
+      <c r="AQ122" s="15">
+        <f t="shared" si="27"/>
+        <v>10.9154</v>
+      </c>
+      <c r="AR122" s="15">
+        <f t="shared" si="28"/>
+        <v>11.5212</v>
+      </c>
       <c r="AS122" s="15"/>
       <c r="AT122" s="15"/>
       <c r="AU122" s="15"/>
@@ -21254,7 +21968,7 @@
         <v>822.5</v>
       </c>
       <c r="L123" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-738.822</v>
       </c>
       <c r="M123" s="15"/>
@@ -21276,17 +21990,17 @@
       <c r="V123" s="15"/>
       <c r="W123" s="15"/>
       <c r="X123" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>16.735599999999998</v>
       </c>
       <c r="Y123" s="4"/>
       <c r="Z123" s="4">
         <v>500</v>
       </c>
-      <c r="AA123" s="25"/>
-      <c r="AB123" s="25"/>
+      <c r="AA123" s="15"/>
+      <c r="AB123" s="15"/>
       <c r="AC123" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>161.64343077033391</v>
       </c>
       <c r="AD123" s="15">
@@ -21325,11 +22039,17 @@
       </c>
       <c r="AO123" s="15"/>
       <c r="AP123" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>500</v>
       </c>
-      <c r="AQ123" s="15"/>
-      <c r="AR123" s="15"/>
+      <c r="AQ123" s="15">
+        <f t="shared" si="27"/>
+        <v>16.735599999999998</v>
+      </c>
+      <c r="AR123" s="15">
+        <f t="shared" si="28"/>
+        <v>189.98179999999999</v>
+      </c>
       <c r="AS123" s="15"/>
       <c r="AT123" s="15"/>
       <c r="AU123" s="15"/>
@@ -21371,7 +22091,7 @@
         <v>160</v>
       </c>
       <c r="L124" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-17</v>
       </c>
       <c r="M124" s="15"/>
@@ -21390,22 +22110,22 @@
       <c r="V124" s="15"/>
       <c r="W124" s="15"/>
       <c r="X124" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>28.6</v>
       </c>
       <c r="Y124" s="4"/>
       <c r="Z124" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA124" s="25"/>
-      <c r="AB124" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA124" s="15"/>
+      <c r="AB124" s="15"/>
       <c r="AC124" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>26.041958041958047</v>
       </c>
       <c r="AD124" s="15">
-        <f t="shared" ref="AD124:AD132" si="35">(F124+O124+P124+R124+S124+T124+U124+V124+W124)/X124</f>
+        <f t="shared" ref="AD124:AD132" si="39">(F124+O124+P124+R124+S124+T124+U124+V124+W124)/X124</f>
         <v>26.041958041958047</v>
       </c>
       <c r="AE124" s="15">
@@ -21440,11 +22160,17 @@
       </c>
       <c r="AO124" s="15"/>
       <c r="AP124" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ124" s="15"/>
-      <c r="AR124" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ124" s="15">
+        <f t="shared" si="27"/>
+        <v>7.15</v>
+      </c>
+      <c r="AR124" s="15">
+        <f t="shared" si="28"/>
+        <v>14.4</v>
+      </c>
       <c r="AS124" s="15"/>
       <c r="AT124" s="15"/>
       <c r="AU124" s="15"/>
@@ -21486,7 +22212,7 @@
         <v>143</v>
       </c>
       <c r="L125" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-11</v>
       </c>
       <c r="M125" s="15"/>
@@ -21505,22 +22231,22 @@
       <c r="V125" s="15"/>
       <c r="W125" s="15"/>
       <c r="X125" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>26.4</v>
       </c>
       <c r="Y125" s="4"/>
       <c r="Z125" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA125" s="25"/>
-      <c r="AB125" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA125" s="15"/>
+      <c r="AB125" s="15"/>
       <c r="AC125" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>15.681818181818183</v>
       </c>
       <c r="AD125" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>15.681818181818183</v>
       </c>
       <c r="AE125" s="15">
@@ -21555,11 +22281,17 @@
       </c>
       <c r="AO125" s="15"/>
       <c r="AP125" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ125" s="15"/>
-      <c r="AR125" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ125" s="15">
+        <f t="shared" si="27"/>
+        <v>8.58</v>
+      </c>
+      <c r="AR125" s="15">
+        <f t="shared" si="28"/>
+        <v>11.375</v>
+      </c>
       <c r="AS125" s="15"/>
       <c r="AT125" s="15"/>
       <c r="AU125" s="15"/>
@@ -21601,7 +22333,7 @@
         <v>247</v>
       </c>
       <c r="L126" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>6</v>
       </c>
       <c r="M126" s="15"/>
@@ -21620,22 +22352,22 @@
       <c r="V126" s="15"/>
       <c r="W126" s="15"/>
       <c r="X126" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>50.6</v>
       </c>
       <c r="Y126" s="4"/>
       <c r="Z126" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA126" s="25"/>
-      <c r="AB126" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA126" s="15"/>
+      <c r="AB126" s="15"/>
       <c r="AC126" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>19.09090909090909</v>
       </c>
       <c r="AD126" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>19.09090909090909</v>
       </c>
       <c r="AE126" s="15">
@@ -21670,11 +22402,17 @@
       </c>
       <c r="AO126" s="15"/>
       <c r="AP126" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ126" s="15"/>
-      <c r="AR126" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ126" s="15">
+        <f t="shared" si="27"/>
+        <v>12.65</v>
+      </c>
+      <c r="AR126" s="15">
+        <f t="shared" si="28"/>
+        <v>17.149999999999999</v>
+      </c>
       <c r="AS126" s="15"/>
       <c r="AT126" s="15"/>
       <c r="AU126" s="15"/>
@@ -21714,7 +22452,7 @@
         <v>25</v>
       </c>
       <c r="L127" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-30</v>
       </c>
       <c r="M127" s="15"/>
@@ -21735,24 +22473,24 @@
       <c r="V127" s="15"/>
       <c r="W127" s="15"/>
       <c r="X127" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-1</v>
       </c>
       <c r="Y127" s="4">
         <v>100</v>
       </c>
       <c r="Z127" s="4">
-        <f t="shared" ref="Z127:Z128" si="36">Y127*1.5</f>
+        <f t="shared" ref="Z127:Z128" si="40">Y127*1.5</f>
         <v>150</v>
       </c>
-      <c r="AA127" s="25"/>
-      <c r="AB127" s="25"/>
+      <c r="AA127" s="15"/>
+      <c r="AB127" s="15"/>
       <c r="AC127" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-197</v>
       </c>
       <c r="AD127" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>-47</v>
       </c>
       <c r="AE127" s="15">
@@ -21787,11 +22525,17 @@
       </c>
       <c r="AO127" s="15"/>
       <c r="AP127" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>45</v>
       </c>
-      <c r="AQ127" s="15"/>
-      <c r="AR127" s="15"/>
+      <c r="AQ127" s="15">
+        <f t="shared" si="27"/>
+        <v>-0.3</v>
+      </c>
+      <c r="AR127" s="15">
+        <f t="shared" si="28"/>
+        <v>-0.12</v>
+      </c>
       <c r="AS127" s="15"/>
       <c r="AT127" s="15"/>
       <c r="AU127" s="15"/>
@@ -21831,7 +22575,7 @@
         <v>32</v>
       </c>
       <c r="L128" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-36</v>
       </c>
       <c r="M128" s="15"/>
@@ -21854,24 +22598,24 @@
       </c>
       <c r="W128" s="15"/>
       <c r="X128" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.8</v>
       </c>
       <c r="Y128" s="4">
         <v>60</v>
       </c>
       <c r="Z128" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>90</v>
       </c>
-      <c r="AA128" s="25"/>
-      <c r="AB128" s="25"/>
+      <c r="AA128" s="15"/>
+      <c r="AB128" s="15"/>
       <c r="AC128" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-113.75</v>
       </c>
       <c r="AD128" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>-1.25</v>
       </c>
       <c r="AE128" s="15">
@@ -21906,11 +22650,17 @@
       </c>
       <c r="AO128" s="15"/>
       <c r="AP128" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>27</v>
       </c>
-      <c r="AQ128" s="15"/>
-      <c r="AR128" s="15"/>
+      <c r="AQ128" s="15">
+        <f t="shared" si="27"/>
+        <v>-0.24</v>
+      </c>
+      <c r="AR128" s="15">
+        <f t="shared" si="28"/>
+        <v>-0.3</v>
+      </c>
       <c r="AS128" s="15"/>
       <c r="AT128" s="15"/>
       <c r="AU128" s="15"/>
@@ -21952,7 +22702,7 @@
         <v>18.2</v>
       </c>
       <c r="L129" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.33600000000000207</v>
       </c>
       <c r="M129" s="15"/>
@@ -21971,22 +22721,22 @@
       <c r="V129" s="15"/>
       <c r="W129" s="15"/>
       <c r="X129" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>3.7072000000000003</v>
       </c>
       <c r="Y129" s="4"/>
       <c r="Z129" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA129" s="25"/>
-      <c r="AB129" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA129" s="15"/>
+      <c r="AB129" s="15"/>
       <c r="AC129" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>12.016886059559774</v>
       </c>
       <c r="AD129" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>12.016886059559774</v>
       </c>
       <c r="AE129" s="15">
@@ -22021,11 +22771,17 @@
       </c>
       <c r="AO129" s="15"/>
       <c r="AP129" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ129" s="15"/>
-      <c r="AR129" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ129" s="15">
+        <f t="shared" si="27"/>
+        <v>3.7072000000000003</v>
+      </c>
+      <c r="AR129" s="15">
+        <f t="shared" si="28"/>
+        <v>4.2619999999999996</v>
+      </c>
       <c r="AS129" s="15"/>
       <c r="AT129" s="15"/>
       <c r="AU129" s="15"/>
@@ -22059,7 +22815,7 @@
         <v>8</v>
       </c>
       <c r="L130" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-8</v>
       </c>
       <c r="M130" s="15"/>
@@ -22082,24 +22838,24 @@
       </c>
       <c r="W130" s="15"/>
       <c r="X130" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="Y130" s="4">
         <v>40</v>
       </c>
       <c r="Z130" s="4">
-        <f t="shared" ref="Z130:Z131" si="37">Y130*1.5</f>
+        <f t="shared" ref="Z130:Z131" si="41">Y130*1.5</f>
         <v>60</v>
       </c>
-      <c r="AA130" s="25"/>
-      <c r="AB130" s="25"/>
+      <c r="AA130" s="15"/>
+      <c r="AB130" s="15"/>
       <c r="AC130" s="15" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD130" s="15" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE130" s="15">
@@ -22134,11 +22890,17 @@
       </c>
       <c r="AO130" s="15"/>
       <c r="AP130" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>18</v>
       </c>
-      <c r="AQ130" s="15"/>
-      <c r="AR130" s="15"/>
+      <c r="AQ130" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR130" s="15">
+        <f t="shared" si="28"/>
+        <v>-0.06</v>
+      </c>
       <c r="AS130" s="15"/>
       <c r="AT130" s="15"/>
       <c r="AU130" s="15"/>
@@ -22178,7 +22940,7 @@
         <v>21</v>
       </c>
       <c r="L131" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-8</v>
       </c>
       <c r="M131" s="15"/>
@@ -22197,24 +22959,24 @@
       <c r="V131" s="15"/>
       <c r="W131" s="15"/>
       <c r="X131" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>2.6</v>
       </c>
       <c r="Y131" s="4">
         <v>10</v>
       </c>
       <c r="Z131" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
-      <c r="AA131" s="25"/>
-      <c r="AB131" s="25"/>
+      <c r="AA131" s="15"/>
+      <c r="AB131" s="15"/>
       <c r="AC131" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>24.23076923076923</v>
       </c>
       <c r="AD131" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>18.46153846153846</v>
       </c>
       <c r="AE131" s="15">
@@ -22249,11 +23011,17 @@
       </c>
       <c r="AO131" s="15"/>
       <c r="AP131" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2</v>
       </c>
-      <c r="AQ131" s="15"/>
-      <c r="AR131" s="15"/>
+      <c r="AQ131" s="15">
+        <f t="shared" si="27"/>
+        <v>0.312</v>
+      </c>
+      <c r="AR131" s="15">
+        <f t="shared" si="28"/>
+        <v>0.96</v>
+      </c>
       <c r="AS131" s="15"/>
       <c r="AT131" s="15"/>
       <c r="AU131" s="15"/>
@@ -22293,7 +23061,7 @@
         <v>81</v>
       </c>
       <c r="L132" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>-4</v>
       </c>
       <c r="M132" s="11"/>
@@ -22312,22 +23080,22 @@
       <c r="V132" s="11"/>
       <c r="W132" s="11"/>
       <c r="X132" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>15.4</v>
       </c>
       <c r="Y132" s="13"/>
       <c r="Z132" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA132" s="25"/>
-      <c r="AB132" s="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AA132" s="15"/>
+      <c r="AB132" s="15"/>
       <c r="AC132" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.0259740259740262</v>
       </c>
       <c r="AD132" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>9.0259740259740262</v>
       </c>
       <c r="AE132" s="11">
@@ -22362,11 +23130,17 @@
       </c>
       <c r="AO132" s="11"/>
       <c r="AP132" s="15">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AQ132" s="15"/>
-      <c r="AR132" s="15"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AQ132" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AR132" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AS132" s="15"/>
       <c r="AT132" s="15"/>
       <c r="AU132" s="15"/>
